--- a/data/states/nj/raw_download.xlsx
+++ b/data/states/nj/raw_download.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="101" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04DF2683-3B3D-475B-B0C6-0F5FD85C5354}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17890984-6F5F-4560-942A-A6A9AE2D77E4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7618" uniqueCount="3263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7621" uniqueCount="3264">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14230,6 +14230,9 @@
   </si>
   <si>
     <t>11/1/26 - 12/31/26</t>
+  </si>
+  <si>
+    <t>Hudson County</t>
   </si>
 </sst>
 </file>
@@ -17129,10 +17132,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17747,7 +17746,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -19268,6 +19267,23 @@
       </c>
       <c r="E89" s="49">
         <v>62</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="60" t="s">
+        <v>3239</v>
+      </c>
+      <c r="B90" s="60" t="s">
+        <v>3263</v>
+      </c>
+      <c r="C90" s="58" t="s">
+        <v>364</v>
+      </c>
+      <c r="D90" s="50">
+        <v>46326</v>
+      </c>
+      <c r="E90" s="49">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/data/states/nj/raw_download.xlsx
+++ b/data/states/nj/raw_download.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17890984-6F5F-4560-942A-A6A9AE2D77E4}"/>
+  <xr:revisionPtr revIDLastSave="108" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F735B94-BC50-4832-AEE0-F3779838E328}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7621" uniqueCount="3264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7625" uniqueCount="3266">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14233,6 +14233,12 @@
   </si>
   <si>
     <t>Hudson County</t>
+  </si>
+  <si>
+    <t>Gerresheimer</t>
+  </si>
+  <si>
+    <t>9/1/26 - 7/30/27</t>
   </si>
 </sst>
 </file>
@@ -17132,6 +17138,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17746,13 +17756,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E90"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <dimension ref="A1:E91"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17790,7 +17800,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.5">
+    <row r="3" spans="1:5" ht="31.2">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17841,7 +17851,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="47.25">
+    <row r="6" spans="1:5" ht="46.8">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17858,7 +17868,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="47.25">
+    <row r="7" spans="1:5" ht="46.8">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17875,7 +17885,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.5">
+    <row r="8" spans="1:5" ht="31.2">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17892,7 +17902,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17909,7 +17919,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78.75">
+    <row r="10" spans="1:5" ht="78">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -17960,7 +17970,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="47.25">
+    <row r="13" spans="1:5" ht="46.8">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -17977,7 +17987,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.5">
+    <row r="14" spans="1:5" ht="31.2">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -18062,7 +18072,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -18130,7 +18140,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="63">
+    <row r="23" spans="1:5" ht="62.4">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -18147,7 +18157,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.5">
+    <row r="24" spans="1:5" ht="31.2">
       <c r="A24" s="48" t="s">
         <v>3184</v>
       </c>
@@ -18164,7 +18174,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="47.25">
+    <row r="25" spans="1:5" ht="46.8">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18249,7 +18259,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.5">
+    <row r="30" spans="1:5" ht="31.2">
       <c r="A30" s="60" t="s">
         <v>3193</v>
       </c>
@@ -18555,7 +18565,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.5">
+    <row r="48" spans="1:5" ht="31.2">
       <c r="A48" s="48" t="s">
         <v>3217</v>
       </c>
@@ -18776,7 +18786,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="31.5">
+    <row r="61" spans="1:5" ht="31.2">
       <c r="A61" s="63" t="s">
         <v>3231</v>
       </c>
@@ -18844,7 +18854,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="31.5">
+    <row r="65" spans="1:5" ht="31.2">
       <c r="A65" s="63" t="s">
         <v>3235</v>
       </c>
@@ -18912,7 +18922,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.5">
+    <row r="69" spans="1:5" ht="31.2">
       <c r="A69" s="60" t="s">
         <v>3239</v>
       </c>
@@ -18963,7 +18973,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="31.5">
+    <row r="72" spans="1:5" ht="31.2">
       <c r="A72" s="60" t="s">
         <v>3243</v>
       </c>
@@ -18980,7 +18990,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="31.5">
+    <row r="73" spans="1:5" ht="31.2">
       <c r="A73" s="60" t="s">
         <v>3243</v>
       </c>
@@ -18997,7 +19007,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="31.5">
+    <row r="74" spans="1:5" ht="31.2">
       <c r="A74" s="63" t="s">
         <v>3244</v>
       </c>
@@ -19014,7 +19024,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="31.5">
+    <row r="75" spans="1:5" ht="31.2">
       <c r="A75" s="48" t="s">
         <v>3245</v>
       </c>
@@ -19048,7 +19058,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="63">
+    <row r="77" spans="1:5" ht="62.4">
       <c r="A77" s="60" t="s">
         <v>3248</v>
       </c>
@@ -19116,7 +19126,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.5">
+    <row r="81" spans="1:5" ht="31.2">
       <c r="A81" s="60" t="s">
         <v>3253</v>
       </c>
@@ -19167,7 +19177,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="31.5">
+    <row r="84" spans="1:5" ht="31.2">
       <c r="A84" s="60" t="s">
         <v>3257</v>
       </c>
@@ -19184,7 +19194,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="31.5">
+    <row r="85" spans="1:5" ht="31.2">
       <c r="A85" s="60" t="s">
         <v>3258</v>
       </c>
@@ -19201,7 +19211,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="31.5">
+    <row r="86" spans="1:5" ht="31.2">
       <c r="A86" s="60" t="s">
         <v>3243</v>
       </c>
@@ -19218,7 +19228,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="31.5">
+    <row r="87" spans="1:5" ht="31.2">
       <c r="A87" s="60" t="s">
         <v>3231</v>
       </c>
@@ -19284,6 +19294,23 @@
       </c>
       <c r="E90" s="49">
         <v>59</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="48" t="s">
+        <v>3264</v>
+      </c>
+      <c r="B91" s="48" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C91" s="49" t="s">
+        <v>364</v>
+      </c>
+      <c r="D91" s="50" t="s">
+        <v>3265</v>
+      </c>
+      <c r="E91" s="48">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -19302,12 +19329,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="50.88671875" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20262,7 +20289,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5" ht="28.8">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -20381,7 +20408,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="30">
+    <row r="64" spans="1:5" ht="28.8">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -20792,12 +20819,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="58.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20834,7 +20861,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30">
+    <row r="3" spans="1:5" ht="28.8">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -20868,7 +20895,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30">
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -20987,7 +21014,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30">
+    <row r="12" spans="1:5" ht="28.8">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -21055,7 +21082,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5" ht="28.8">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -21089,7 +21116,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -21531,7 +21558,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -21789,12 +21816,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -21899,7 +21926,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5" ht="28.8">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -21967,7 +21994,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="30">
+    <row r="11" spans="1:5" ht="28.8">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -22018,7 +22045,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="30">
+    <row r="14" spans="1:5" ht="28.8">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -22086,7 +22113,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -22460,7 +22487,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -22528,7 +22555,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -22698,7 +22725,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -22953,7 +22980,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -23344,7 +23371,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="30">
+    <row r="92" spans="1:5" ht="28.8">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -23412,7 +23439,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="30">
+    <row r="96" spans="1:5" ht="28.8">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -23514,7 +23541,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="45">
+    <row r="102" spans="1:5" ht="28.8">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -23531,7 +23558,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="30">
+    <row r="103" spans="1:5" ht="28.8">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -23582,7 +23609,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -23650,7 +23677,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5" ht="28.8">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -23684,7 +23711,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="30">
+    <row r="112" spans="1:5">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -23752,7 +23779,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5" ht="28.8">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -23786,7 +23813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="30">
+    <row r="118" spans="1:5" ht="28.8">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -23803,7 +23830,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -23871,7 +23898,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="30">
+    <row r="123" spans="1:5">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -24007,7 +24034,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="30">
+    <row r="131" spans="1:5">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -24177,7 +24204,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="30">
+    <row r="141" spans="1:5" ht="28.8">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -24364,7 +24391,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="30">
+    <row r="152" spans="1:5">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -24707,13 +24734,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25770,7 +25797,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="30">
+    <row r="63" spans="1:5">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -25804,7 +25831,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -25923,7 +25950,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="30">
+    <row r="72" spans="1:5" ht="28.8">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -25957,7 +25984,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -26212,7 +26239,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="30">
+    <row r="89" spans="1:5" ht="28.8">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -26280,7 +26307,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="30">
+    <row r="93" spans="1:5" ht="28.8">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -26589,13 +26616,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -26717,7 +26744,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="30">
+    <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -27142,7 +27169,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="30">
+    <row r="33" spans="1:5" ht="28.8">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -27550,7 +27577,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -27893,13 +27920,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -28393,7 +28420,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -28767,7 +28794,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5" ht="28.8">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -28988,7 +29015,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -29022,7 +29049,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5" ht="28.8">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -29501,13 +29528,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -29527,7 +29554,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30">
+    <row r="2" spans="1:5" ht="28.8">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -29595,7 +29622,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -29646,7 +29673,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -29765,7 +29792,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -29901,7 +29928,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -30003,7 +30030,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -30020,7 +30047,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="30">
+    <row r="31" spans="1:5" ht="28.8">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -30037,7 +30064,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="45">
+    <row r="32" spans="1:5" ht="28.8">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -30139,7 +30166,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -30207,7 +30234,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -30377,7 +30404,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -30428,7 +30455,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="30">
+    <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -30700,7 +30727,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="30">
+    <row r="71" spans="1:5" ht="28.8">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -30887,7 +30914,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="30">
+    <row r="82" spans="1:5" ht="28.8">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -31213,13 +31240,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -31324,7 +31351,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -33027,13 +33054,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -34158,7 +34185,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -34175,7 +34202,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="30">
+    <row r="68" spans="1:5">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -35229,7 +35256,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="30">
+    <row r="130" spans="1:5" ht="28.8">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -35288,13 +35315,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -37698,16 +37725,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" customWidth="1"/>
-    <col min="2" max="2" width="31.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.88671875" customWidth="1"/>
+    <col min="2" max="2" width="31.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75">
+    <row r="1" spans="1:5" ht="15.6">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -37724,7 +37751,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.5">
+    <row r="2" spans="1:5" ht="31.2">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37741,7 +37768,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75">
+    <row r="3" spans="1:5" ht="15.6">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -37758,7 +37785,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.5">
+    <row r="4" spans="1:5" ht="31.2">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -37775,7 +37802,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="47.25">
+    <row r="5" spans="1:5" ht="46.8">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -37792,7 +37819,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75">
+    <row r="6" spans="1:5" ht="15.6">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -37809,7 +37836,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75">
+    <row r="7" spans="1:5" ht="15.6">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -37826,7 +37853,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75">
+    <row r="8" spans="1:5" ht="15.6">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -37843,7 +37870,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -37860,7 +37887,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75">
+    <row r="10" spans="1:5" ht="15.6">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -37877,7 +37904,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.5">
+    <row r="11" spans="1:5" ht="31.2">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37894,7 +37921,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="94.5">
+    <row r="12" spans="1:5" ht="93.6">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -37911,7 +37938,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75">
+    <row r="13" spans="1:5" ht="15.6">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -37928,7 +37955,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75">
+    <row r="14" spans="1:5" ht="15.6">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -37945,7 +37972,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75">
+    <row r="15" spans="1:5" ht="15.6">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -37962,7 +37989,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75">
+    <row r="16" spans="1:5" ht="15.6">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -37979,7 +38006,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="63">
+    <row r="17" spans="1:5" ht="62.4">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -37996,7 +38023,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="63">
+    <row r="18" spans="1:5" ht="62.4">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -38013,7 +38040,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -38030,7 +38057,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75">
+    <row r="20" spans="1:5" ht="15.6">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -38047,7 +38074,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="47.25">
+    <row r="21" spans="1:5" ht="46.8">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -38064,7 +38091,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75">
+    <row r="22" spans="1:5" ht="15.6">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -38081,7 +38108,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75">
+    <row r="23" spans="1:5" ht="15.6">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -38098,7 +38125,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75">
+    <row r="24" spans="1:5" ht="15.6">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -38115,7 +38142,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75">
+    <row r="25" spans="1:5" ht="15.6">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -38132,7 +38159,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75">
+    <row r="26" spans="1:5" ht="15.6">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -38149,7 +38176,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.5">
+    <row r="27" spans="1:5" ht="31.2">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -38166,7 +38193,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75">
+    <row r="28" spans="1:5" ht="15.6">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -38183,7 +38210,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75">
+    <row r="29" spans="1:5" ht="15.6">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -38200,7 +38227,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75">
+    <row r="30" spans="1:5" ht="15.6">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -38217,7 +38244,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="94.5">
+    <row r="31" spans="1:5" ht="93.6">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38234,7 +38261,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="63">
+    <row r="32" spans="1:5" ht="62.4">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -38251,7 +38278,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75">
+    <row r="33" spans="1:5" ht="15.6">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -38268,7 +38295,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="63">
+    <row r="34" spans="1:5" ht="62.4">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -38285,7 +38312,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75">
+    <row r="35" spans="1:5" ht="15.6">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -38302,7 +38329,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.75">
+    <row r="36" spans="1:5" ht="15.6">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -38319,7 +38346,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75">
+    <row r="37" spans="1:5" ht="15.6">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -38336,7 +38363,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="63">
+    <row r="38" spans="1:5" ht="62.4">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -38353,7 +38380,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75">
+    <row r="39" spans="1:5" ht="15.6">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -38370,7 +38397,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.75">
+    <row r="40" spans="1:5" ht="15.6">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -38387,7 +38414,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75">
+    <row r="41" spans="1:5" ht="15.6">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -38404,7 +38431,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75">
+    <row r="42" spans="1:5" ht="15.6">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -38421,7 +38448,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.75">
+    <row r="43" spans="1:5" ht="15.6">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -38438,7 +38465,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.75">
+    <row r="44" spans="1:5" ht="15.6">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -38455,7 +38482,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="47.25">
+    <row r="45" spans="1:5" ht="46.8">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -38472,7 +38499,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.75">
+    <row r="46" spans="1:5" ht="15.6">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -38489,7 +38516,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.75">
+    <row r="47" spans="1:5" ht="15.6">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -38506,7 +38533,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.5">
+    <row r="48" spans="1:5" ht="31.2">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -38523,7 +38550,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.75">
+    <row r="49" spans="1:5" ht="15.6">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -38540,7 +38567,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.5">
+    <row r="50" spans="1:5" ht="31.2">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38557,7 +38584,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.75">
+    <row r="51" spans="1:5" ht="15.6">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -38574,7 +38601,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.75">
+    <row r="52" spans="1:5" ht="15.6">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38591,7 +38618,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.75">
+    <row r="53" spans="1:5" ht="15.6">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -38608,7 +38635,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.5">
+    <row r="54" spans="1:5" ht="31.2">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38625,7 +38652,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.75">
+    <row r="55" spans="1:5" ht="15.6">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -38642,7 +38669,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="94.5">
+    <row r="56" spans="1:5" ht="93.6">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -38659,7 +38686,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.75">
+    <row r="57" spans="1:5" ht="15.6">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -38676,7 +38703,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.75">
+    <row r="58" spans="1:5" ht="15.6">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -38693,7 +38720,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.75">
+    <row r="59" spans="1:5" ht="15.6">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -38710,7 +38737,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.75">
+    <row r="60" spans="1:5" ht="15.6">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -38727,7 +38754,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="47.25">
+    <row r="61" spans="1:5" ht="46.8">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38744,7 +38771,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.75">
+    <row r="62" spans="1:5" ht="15.6">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -38761,7 +38788,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.75">
+    <row r="63" spans="1:5" ht="15.6">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -38778,7 +38805,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.75">
+    <row r="64" spans="1:5" ht="15.6">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -38795,7 +38822,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.75">
+    <row r="65" spans="1:5" ht="15.6">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38812,7 +38839,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.75">
+    <row r="66" spans="1:5" ht="15.6">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -38829,7 +38856,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.75">
+    <row r="67" spans="1:5" ht="15.6">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -38846,7 +38873,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.75">
+    <row r="68" spans="1:5" ht="15.6">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -38863,7 +38890,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.75">
+    <row r="69" spans="1:5" ht="15.6">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38880,7 +38907,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.5">
+    <row r="70" spans="1:5" ht="31.2">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38897,7 +38924,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.75">
+    <row r="71" spans="1:5" ht="15.6">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -38914,7 +38941,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.75">
+    <row r="72" spans="1:5" ht="15.6">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38931,7 +38958,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.75">
+    <row r="73" spans="1:5" ht="15.6">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -38948,7 +38975,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="47.25">
+    <row r="74" spans="1:5" ht="46.8">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38965,7 +38992,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.75">
+    <row r="75" spans="1:5" ht="15.6">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -38982,7 +39009,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.75">
+    <row r="76" spans="1:5" ht="15.6">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -38999,7 +39026,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.5">
+    <row r="77" spans="1:5" ht="31.2">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -39016,7 +39043,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.5">
+    <row r="78" spans="1:5" ht="31.2">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -39033,7 +39060,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.5">
+    <row r="79" spans="1:5" ht="31.2">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -39050,7 +39077,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.75">
+    <row r="80" spans="1:5" ht="15.6">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -39067,7 +39094,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.5">
+    <row r="81" spans="1:5" ht="31.2">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -39084,7 +39111,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.75">
+    <row r="82" spans="1:5" ht="15.6">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -39101,7 +39128,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.5">
+    <row r="83" spans="1:5" ht="31.2">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -39118,7 +39145,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="47.25">
+    <row r="84" spans="1:5" ht="46.8">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -39135,7 +39162,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.75">
+    <row r="85" spans="1:5" ht="15.6">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -39152,7 +39179,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.75">
+    <row r="86" spans="1:5" ht="15.6">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -39169,7 +39196,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.75">
+    <row r="87" spans="1:5" ht="15.6">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -39186,7 +39213,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.75">
+    <row r="88" spans="1:5" ht="15.6">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -39203,7 +39230,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.75">
+    <row r="89" spans="1:5" ht="15.6">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -39220,7 +39247,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.75">
+    <row r="90" spans="1:5" ht="15.6">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -39237,7 +39264,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="47.25">
+    <row r="91" spans="1:5" ht="46.8">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -39254,7 +39281,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.5">
+    <row r="92" spans="1:5" ht="31.2">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -39271,7 +39298,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.5">
+    <row r="93" spans="1:5" ht="31.2">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -39288,7 +39315,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -39305,7 +39332,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -39322,7 +39349,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.75">
+    <row r="96" spans="1:5" ht="15.6">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -39339,7 +39366,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.75">
+    <row r="97" spans="1:5" ht="15.6">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -39356,7 +39383,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -39373,7 +39400,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.5">
+    <row r="99" spans="1:5" ht="31.2">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -39390,7 +39417,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.75">
+    <row r="100" spans="1:5" ht="15.6">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -39407,7 +39434,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.75">
+    <row r="101" spans="1:5" ht="15.6">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -39424,7 +39451,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.5">
+    <row r="102" spans="1:5" ht="31.2">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -39441,7 +39468,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.75">
+    <row r="103" spans="1:5" ht="15.6">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -39458,7 +39485,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.75">
+    <row r="104" spans="1:5" ht="15.6">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -39475,7 +39502,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.75">
+    <row r="105" spans="1:5" ht="15.6">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -39492,7 +39519,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.75">
+    <row r="106" spans="1:5" ht="15.6">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -39509,7 +39536,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.75">
+    <row r="107" spans="1:5" ht="15.6">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -39526,7 +39553,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.75">
+    <row r="108" spans="1:5" ht="15.6">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -39543,7 +39570,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.5">
+    <row r="109" spans="1:5" ht="31.2">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -39560,7 +39587,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.75">
+    <row r="110" spans="1:5" ht="15.6">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -39596,14 +39623,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41208,14 +41235,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41845,7 +41872,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -42928,14 +42955,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -44667,13 +44694,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46411,14 +46438,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="32"/>
+    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46557,7 +46584,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="47.25">
+    <row r="9" spans="1:5" ht="46.8">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -46574,7 +46601,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="47.25">
+    <row r="10" spans="1:5" ht="46.8">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -46625,7 +46652,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.5">
+    <row r="13" spans="1:5" ht="31.2">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -46693,7 +46720,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="47.25">
+    <row r="17" spans="1:5" ht="46.8">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -46744,7 +46771,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.5">
+    <row r="20" spans="1:5" ht="31.2">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -46778,7 +46805,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.5">
+    <row r="22" spans="1:5" ht="31.2">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -46999,7 +47026,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="63">
+    <row r="35" spans="1:5" ht="62.4">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -47067,7 +47094,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.5">
+    <row r="39" spans="1:5" ht="31.2">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47135,7 +47162,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="31.2">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -47339,7 +47366,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78.75">
+    <row r="55" spans="1:5" ht="78">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -47577,7 +47604,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.5">
+    <row r="69" spans="1:5" ht="31.2">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47645,7 +47672,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="63">
+    <row r="73" spans="1:5" ht="62.4">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -47891,7 +47918,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.5">
+    <row r="88" spans="1:5" ht="31.2">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -47993,7 +48020,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -48010,7 +48037,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -48044,7 +48071,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78.75">
+    <row r="97" spans="1:5" ht="78">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -48061,7 +48088,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -48112,7 +48139,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.5">
+    <row r="101" spans="1:5" ht="31.2">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -48231,7 +48258,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="63">
+    <row r="108" spans="1:5" ht="62.4">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -48302,14 +48329,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -49553,7 +49580,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5" ht="28.8">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -49842,7 +49869,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="45">
+    <row r="91" spans="1:5" ht="43.2">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -50080,7 +50107,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="75">
+    <row r="105" spans="1:5" ht="72">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -50097,7 +50124,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -50131,7 +50158,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="30">
+    <row r="108" spans="1:5" ht="28.8">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -50252,14 +50279,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51009,14 +51036,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51410,7 +51437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5" ht="28.8">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -51597,7 +51624,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="30">
+    <row r="35" spans="1:13" ht="28.8">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -51893,13 +51920,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51987,7 +52014,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -52225,7 +52252,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="30">
+    <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -52548,7 +52575,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="30">
+    <row r="39" spans="1:5" ht="28.8">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -52565,7 +52592,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -52582,7 +52609,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="30">
+    <row r="41" spans="1:5" ht="28.8">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -52599,7 +52626,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -52633,7 +52660,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -52871,7 +52898,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="30">
+    <row r="58" spans="1:5">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -52888,7 +52915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="30">
+    <row r="59" spans="1:5" ht="28.8">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -53058,7 +53085,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -53143,7 +53170,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -53296,7 +53323,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="30">
+    <row r="83" spans="1:5">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -53483,7 +53510,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="30">
+    <row r="94" spans="1:5">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -53585,7 +53612,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="30">
+    <row r="100" spans="1:5">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -53602,7 +53629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="30">
+    <row r="101" spans="1:5" ht="28.8">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -53755,7 +53782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -53772,7 +53799,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="30">
+    <row r="111" spans="1:5" ht="28.8">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -53857,7 +53884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -53908,7 +53935,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -54180,7 +54207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="30">
+    <row r="135" spans="1:5">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -54333,7 +54360,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="30">
+    <row r="144" spans="1:5" ht="28.8">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -54401,7 +54428,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="30">
+    <row r="148" spans="1:5">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -54435,7 +54462,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="30">
+    <row r="150" spans="1:5" ht="28.8">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -54452,7 +54479,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="30">
+    <row r="151" spans="1:5">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -54707,7 +54734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="30">
+    <row r="166" spans="1:5">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -54877,7 +54904,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="30">
+    <row r="176" spans="1:5">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -54928,7 +54955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="30">
+    <row r="179" spans="1:5" ht="28.8">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -55013,7 +55040,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="30">
+    <row r="184" spans="1:5">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -55098,7 +55125,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="30">
+    <row r="189" spans="1:5">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -55676,7 +55703,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="30">
+    <row r="223" spans="1:5">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -56036,12 +56063,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -56180,7 +56207,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -56707,7 +56734,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -57047,7 +57074,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="30">
+    <row r="60" spans="1:5" ht="28.8">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -57064,7 +57091,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="30">
+    <row r="61" spans="1:5" ht="28.8">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -57081,7 +57108,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="30">
+    <row r="62" spans="1:5" ht="28.8">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -57166,7 +57193,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -57319,7 +57346,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="30">
+    <row r="76" spans="1:5" ht="28.8">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -57336,7 +57363,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="30">
+    <row r="77" spans="1:5" ht="28.8">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -57387,7 +57414,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="30">
+    <row r="80" spans="1:5" ht="28.8">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -57509,12 +57536,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -57993,7 +58020,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="30">
+    <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -58418,7 +58445,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>

--- a/data/states/nj/raw_download.xlsx
+++ b/data/states/nj/raw_download.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="108" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F735B94-BC50-4832-AEE0-F3779838E328}"/>
+  <xr:revisionPtr revIDLastSave="115" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E52F3F1-84FF-4EC7-B610-F2B9C57D3588}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7625" uniqueCount="3266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7628" uniqueCount="3267">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14239,6 +14239,9 @@
   </si>
   <si>
     <t>9/1/26 - 7/30/27</t>
+  </si>
+  <si>
+    <t>Grocery Delivery E-Services USA, Inc DBA Hello Fresh</t>
   </si>
 </sst>
 </file>
@@ -17138,10 +17141,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17756,13 +17755,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E91"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <dimension ref="A1:E92"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.33203125" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17800,7 +17799,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.2">
+    <row r="3" spans="1:5" ht="31.5">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17851,7 +17850,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="46.8">
+    <row r="6" spans="1:5" ht="47.25">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17868,7 +17867,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="46.8">
+    <row r="7" spans="1:5" ht="47.25">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17885,7 +17884,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.2">
+    <row r="8" spans="1:5" ht="31.5">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17902,7 +17901,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17919,7 +17918,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78">
+    <row r="10" spans="1:5" ht="78.75">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -17970,7 +17969,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="46.8">
+    <row r="13" spans="1:5" ht="47.25">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -17987,7 +17986,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.2">
+    <row r="14" spans="1:5" ht="31.5">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -18072,7 +18071,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -18140,7 +18139,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="62.4">
+    <row r="23" spans="1:5" ht="63">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -18157,7 +18156,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.2">
+    <row r="24" spans="1:5" ht="31.5">
       <c r="A24" s="48" t="s">
         <v>3184</v>
       </c>
@@ -18174,7 +18173,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="46.8">
+    <row r="25" spans="1:5" ht="47.25">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18259,7 +18258,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.2">
+    <row r="30" spans="1:5" ht="31.5">
       <c r="A30" s="60" t="s">
         <v>3193</v>
       </c>
@@ -18565,7 +18564,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.2">
+    <row r="48" spans="1:5" ht="31.5">
       <c r="A48" s="48" t="s">
         <v>3217</v>
       </c>
@@ -18786,7 +18785,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="31.2">
+    <row r="61" spans="1:5" ht="31.5">
       <c r="A61" s="63" t="s">
         <v>3231</v>
       </c>
@@ -18854,7 +18853,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="31.2">
+    <row r="65" spans="1:5" ht="31.5">
       <c r="A65" s="63" t="s">
         <v>3235</v>
       </c>
@@ -18922,7 +18921,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.2">
+    <row r="69" spans="1:5" ht="31.5">
       <c r="A69" s="60" t="s">
         <v>3239</v>
       </c>
@@ -18973,7 +18972,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="31.2">
+    <row r="72" spans="1:5" ht="31.5">
       <c r="A72" s="60" t="s">
         <v>3243</v>
       </c>
@@ -18990,7 +18989,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="31.2">
+    <row r="73" spans="1:5" ht="31.5">
       <c r="A73" s="60" t="s">
         <v>3243</v>
       </c>
@@ -19007,7 +19006,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="31.2">
+    <row r="74" spans="1:5" ht="31.5">
       <c r="A74" s="63" t="s">
         <v>3244</v>
       </c>
@@ -19024,7 +19023,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="31.2">
+    <row r="75" spans="1:5" ht="31.5">
       <c r="A75" s="48" t="s">
         <v>3245</v>
       </c>
@@ -19058,7 +19057,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="62.4">
+    <row r="77" spans="1:5" ht="63">
       <c r="A77" s="60" t="s">
         <v>3248</v>
       </c>
@@ -19126,7 +19125,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.2">
+    <row r="81" spans="1:5" ht="31.5">
       <c r="A81" s="60" t="s">
         <v>3253</v>
       </c>
@@ -19177,7 +19176,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="31.2">
+    <row r="84" spans="1:5" ht="31.5">
       <c r="A84" s="60" t="s">
         <v>3257</v>
       </c>
@@ -19194,7 +19193,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="31.2">
+    <row r="85" spans="1:5" ht="31.5">
       <c r="A85" s="60" t="s">
         <v>3258</v>
       </c>
@@ -19211,7 +19210,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="31.2">
+    <row r="86" spans="1:5" ht="31.5">
       <c r="A86" s="60" t="s">
         <v>3243</v>
       </c>
@@ -19228,7 +19227,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="31.2">
+    <row r="87" spans="1:5" ht="31.5">
       <c r="A87" s="60" t="s">
         <v>3231</v>
       </c>
@@ -19311,6 +19310,23 @@
       </c>
       <c r="E91" s="48">
         <v>139</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="31.5">
+      <c r="A92" s="60" t="s">
+        <v>3266</v>
+      </c>
+      <c r="B92" s="60" t="s">
+        <v>2955</v>
+      </c>
+      <c r="C92" s="58" t="s">
+        <v>364</v>
+      </c>
+      <c r="D92" s="50">
+        <v>46343</v>
+      </c>
+      <c r="E92" s="49">
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -19329,12 +19345,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="50.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20289,7 +20305,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="28.8">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -20408,7 +20424,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="28.8">
+    <row r="64" spans="1:5" ht="30">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -20819,12 +20835,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.88671875" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="58.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20861,7 +20877,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.8">
+    <row r="3" spans="1:5" ht="30">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -20895,7 +20911,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="30">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -21014,7 +21030,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="28.8">
+    <row r="12" spans="1:5" ht="30">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -21082,7 +21098,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="28.8">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -21116,7 +21132,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -21558,7 +21574,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -21816,12 +21832,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -21926,7 +21942,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="28.8">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -21994,7 +22010,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="28.8">
+    <row r="11" spans="1:5" ht="30">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -22045,7 +22061,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="28.8">
+    <row r="14" spans="1:5" ht="30">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -22113,7 +22129,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -22487,7 +22503,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -22555,7 +22571,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -22725,7 +22741,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -22980,7 +22996,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -23371,7 +23387,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="28.8">
+    <row r="92" spans="1:5" ht="30">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -23439,7 +23455,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="28.8">
+    <row r="96" spans="1:5" ht="30">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -23541,7 +23557,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="28.8">
+    <row r="102" spans="1:5" ht="45">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -23558,7 +23574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="28.8">
+    <row r="103" spans="1:5" ht="30">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -23609,7 +23625,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -23677,7 +23693,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="28.8">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -23711,7 +23727,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" ht="30">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -23779,7 +23795,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="28.8">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -23813,7 +23829,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="28.8">
+    <row r="118" spans="1:5" ht="30">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -23830,7 +23846,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -23898,7 +23914,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" ht="30">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -24034,7 +24050,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" ht="30">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -24204,7 +24220,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="28.8">
+    <row r="141" spans="1:5" ht="30">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -24391,7 +24407,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" ht="30">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -24734,13 +24750,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25797,7 +25813,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" ht="30">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -25831,7 +25847,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -25950,7 +25966,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="28.8">
+    <row r="72" spans="1:5" ht="30">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -25984,7 +26000,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -26239,7 +26255,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="28.8">
+    <row r="89" spans="1:5" ht="30">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -26307,7 +26323,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="28.8">
+    <row r="93" spans="1:5" ht="30">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -26616,13 +26632,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -26744,7 +26760,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" ht="30">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -27169,7 +27185,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="28.8">
+    <row r="33" spans="1:5" ht="30">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -27577,7 +27593,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -27920,13 +27936,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -28420,7 +28436,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -28794,7 +28810,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="28.8">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -29015,7 +29031,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -29049,7 +29065,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="28.8">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -29528,13 +29544,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -29554,7 +29570,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8">
+    <row r="2" spans="1:5" ht="30">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -29622,7 +29638,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -29673,7 +29689,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -29792,7 +29808,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -29928,7 +29944,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -30030,7 +30046,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -30047,7 +30063,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="28.8">
+    <row r="31" spans="1:5" ht="30">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -30064,7 +30080,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="28.8">
+    <row r="32" spans="1:5" ht="45">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -30166,7 +30182,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -30234,7 +30250,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -30404,7 +30420,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -30455,7 +30471,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" ht="30">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -30727,7 +30743,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="28.8">
+    <row r="71" spans="1:5" ht="30">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -30914,7 +30930,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="28.8">
+    <row r="82" spans="1:5" ht="30">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -31240,13 +31256,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -31351,7 +31367,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -33054,13 +33070,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -34185,7 +34201,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -34202,7 +34218,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" ht="30">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -35256,7 +35272,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="28.8">
+    <row r="130" spans="1:5" ht="30">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -35315,13 +35331,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -37725,16 +37741,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.88671875" customWidth="1"/>
-    <col min="2" max="2" width="31.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="28.33203125" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="31.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="28.28515625" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6">
+    <row r="1" spans="1:5" ht="15.75">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -37751,7 +37767,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.2">
+    <row r="2" spans="1:5" ht="31.5">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37768,7 +37784,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.6">
+    <row r="3" spans="1:5" ht="15.75">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -37785,7 +37801,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.2">
+    <row r="4" spans="1:5" ht="31.5">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -37802,7 +37818,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="46.8">
+    <row r="5" spans="1:5" ht="47.25">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -37819,7 +37835,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.6">
+    <row r="6" spans="1:5" ht="15.75">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -37836,7 +37852,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.6">
+    <row r="7" spans="1:5" ht="15.75">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -37853,7 +37869,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.6">
+    <row r="8" spans="1:5" ht="15.75">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -37870,7 +37886,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -37887,7 +37903,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.6">
+    <row r="10" spans="1:5" ht="15.75">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -37904,7 +37920,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.2">
+    <row r="11" spans="1:5" ht="31.5">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37921,7 +37937,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="93.6">
+    <row r="12" spans="1:5" ht="94.5">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -37938,7 +37954,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.6">
+    <row r="13" spans="1:5" ht="15.75">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -37955,7 +37971,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.6">
+    <row r="14" spans="1:5" ht="15.75">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -37972,7 +37988,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.6">
+    <row r="15" spans="1:5" ht="15.75">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -37989,7 +38005,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.6">
+    <row r="16" spans="1:5" ht="15.75">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38006,7 +38022,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="62.4">
+    <row r="17" spans="1:5" ht="63">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -38023,7 +38039,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="62.4">
+    <row r="18" spans="1:5" ht="63">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -38040,7 +38056,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -38057,7 +38073,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.6">
+    <row r="20" spans="1:5" ht="15.75">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -38074,7 +38090,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="46.8">
+    <row r="21" spans="1:5" ht="47.25">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -38091,7 +38107,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.6">
+    <row r="22" spans="1:5" ht="15.75">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -38108,7 +38124,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.6">
+    <row r="23" spans="1:5" ht="15.75">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -38125,7 +38141,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.6">
+    <row r="24" spans="1:5" ht="15.75">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -38142,7 +38158,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.6">
+    <row r="25" spans="1:5" ht="15.75">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -38159,7 +38175,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.6">
+    <row r="26" spans="1:5" ht="15.75">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -38176,7 +38192,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.2">
+    <row r="27" spans="1:5" ht="31.5">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -38193,7 +38209,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.6">
+    <row r="28" spans="1:5" ht="15.75">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -38210,7 +38226,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.6">
+    <row r="29" spans="1:5" ht="15.75">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -38227,7 +38243,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.6">
+    <row r="30" spans="1:5" ht="15.75">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -38244,7 +38260,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="93.6">
+    <row r="31" spans="1:5" ht="94.5">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38261,7 +38277,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="62.4">
+    <row r="32" spans="1:5" ht="63">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -38278,7 +38294,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.6">
+    <row r="33" spans="1:5" ht="15.75">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -38295,7 +38311,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="62.4">
+    <row r="34" spans="1:5" ht="63">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -38312,7 +38328,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.6">
+    <row r="35" spans="1:5" ht="15.75">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -38329,7 +38345,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.6">
+    <row r="36" spans="1:5" ht="15.75">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -38346,7 +38362,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.6">
+    <row r="37" spans="1:5" ht="15.75">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -38363,7 +38379,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="62.4">
+    <row r="38" spans="1:5" ht="63">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -38380,7 +38396,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.6">
+    <row r="39" spans="1:5" ht="15.75">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -38397,7 +38413,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.6">
+    <row r="40" spans="1:5" ht="15.75">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -38414,7 +38430,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.6">
+    <row r="41" spans="1:5" ht="15.75">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -38431,7 +38447,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.6">
+    <row r="42" spans="1:5" ht="15.75">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -38448,7 +38464,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.6">
+    <row r="43" spans="1:5" ht="15.75">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -38465,7 +38481,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.6">
+    <row r="44" spans="1:5" ht="15.75">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -38482,7 +38498,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="46.8">
+    <row r="45" spans="1:5" ht="47.25">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -38499,7 +38515,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.6">
+    <row r="46" spans="1:5" ht="15.75">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -38516,7 +38532,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.6">
+    <row r="47" spans="1:5" ht="15.75">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -38533,7 +38549,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.2">
+    <row r="48" spans="1:5" ht="31.5">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -38550,7 +38566,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.6">
+    <row r="49" spans="1:5" ht="15.75">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -38567,7 +38583,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.2">
+    <row r="50" spans="1:5" ht="31.5">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38584,7 +38600,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.6">
+    <row r="51" spans="1:5" ht="15.75">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -38601,7 +38617,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.6">
+    <row r="52" spans="1:5" ht="15.75">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38618,7 +38634,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.6">
+    <row r="53" spans="1:5" ht="15.75">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -38635,7 +38651,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.2">
+    <row r="54" spans="1:5" ht="31.5">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38652,7 +38668,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.6">
+    <row r="55" spans="1:5" ht="15.75">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -38669,7 +38685,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="93.6">
+    <row r="56" spans="1:5" ht="94.5">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -38686,7 +38702,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.6">
+    <row r="57" spans="1:5" ht="15.75">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -38703,7 +38719,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.6">
+    <row r="58" spans="1:5" ht="15.75">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -38720,7 +38736,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.6">
+    <row r="59" spans="1:5" ht="15.75">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -38737,7 +38753,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.6">
+    <row r="60" spans="1:5" ht="15.75">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -38754,7 +38770,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="46.8">
+    <row r="61" spans="1:5" ht="47.25">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38771,7 +38787,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.6">
+    <row r="62" spans="1:5" ht="15.75">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -38788,7 +38804,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.6">
+    <row r="63" spans="1:5" ht="15.75">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -38805,7 +38821,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.6">
+    <row r="64" spans="1:5" ht="15.75">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -38822,7 +38838,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.6">
+    <row r="65" spans="1:5" ht="15.75">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38839,7 +38855,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.6">
+    <row r="66" spans="1:5" ht="15.75">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -38856,7 +38872,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.6">
+    <row r="67" spans="1:5" ht="15.75">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -38873,7 +38889,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.6">
+    <row r="68" spans="1:5" ht="15.75">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -38890,7 +38906,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.6">
+    <row r="69" spans="1:5" ht="15.75">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38907,7 +38923,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.2">
+    <row r="70" spans="1:5" ht="31.5">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38924,7 +38940,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.6">
+    <row r="71" spans="1:5" ht="15.75">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -38941,7 +38957,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.6">
+    <row r="72" spans="1:5" ht="15.75">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38958,7 +38974,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.6">
+    <row r="73" spans="1:5" ht="15.75">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -38975,7 +38991,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="46.8">
+    <row r="74" spans="1:5" ht="47.25">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38992,7 +39008,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.6">
+    <row r="75" spans="1:5" ht="15.75">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -39009,7 +39025,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.6">
+    <row r="76" spans="1:5" ht="15.75">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -39026,7 +39042,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.2">
+    <row r="77" spans="1:5" ht="31.5">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -39043,7 +39059,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.2">
+    <row r="78" spans="1:5" ht="31.5">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -39060,7 +39076,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.2">
+    <row r="79" spans="1:5" ht="31.5">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -39077,7 +39093,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.6">
+    <row r="80" spans="1:5" ht="15.75">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -39094,7 +39110,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.2">
+    <row r="81" spans="1:5" ht="31.5">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -39111,7 +39127,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.6">
+    <row r="82" spans="1:5" ht="15.75">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -39128,7 +39144,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.2">
+    <row r="83" spans="1:5" ht="31.5">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -39145,7 +39161,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="46.8">
+    <row r="84" spans="1:5" ht="47.25">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -39162,7 +39178,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.6">
+    <row r="85" spans="1:5" ht="15.75">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -39179,7 +39195,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.6">
+    <row r="86" spans="1:5" ht="15.75">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -39196,7 +39212,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.6">
+    <row r="87" spans="1:5" ht="15.75">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -39213,7 +39229,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.6">
+    <row r="88" spans="1:5" ht="15.75">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -39230,7 +39246,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.6">
+    <row r="89" spans="1:5" ht="15.75">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -39247,7 +39263,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.6">
+    <row r="90" spans="1:5" ht="15.75">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -39264,7 +39280,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="46.8">
+    <row r="91" spans="1:5" ht="47.25">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -39281,7 +39297,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.2">
+    <row r="92" spans="1:5" ht="31.5">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -39298,7 +39314,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.2">
+    <row r="93" spans="1:5" ht="31.5">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -39315,7 +39331,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -39332,7 +39348,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -39349,7 +39365,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.6">
+    <row r="96" spans="1:5" ht="15.75">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -39366,7 +39382,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.6">
+    <row r="97" spans="1:5" ht="15.75">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -39383,7 +39399,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -39400,7 +39416,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.2">
+    <row r="99" spans="1:5" ht="31.5">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -39417,7 +39433,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.6">
+    <row r="100" spans="1:5" ht="15.75">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -39434,7 +39450,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.6">
+    <row r="101" spans="1:5" ht="15.75">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -39451,7 +39467,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.2">
+    <row r="102" spans="1:5" ht="31.5">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -39468,7 +39484,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.6">
+    <row r="103" spans="1:5" ht="15.75">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -39485,7 +39501,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.6">
+    <row r="104" spans="1:5" ht="15.75">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -39502,7 +39518,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.6">
+    <row r="105" spans="1:5" ht="15.75">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -39519,7 +39535,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.6">
+    <row r="106" spans="1:5" ht="15.75">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -39536,7 +39552,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.6">
+    <row r="107" spans="1:5" ht="15.75">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -39553,7 +39569,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.6">
+    <row r="108" spans="1:5" ht="15.75">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -39570,7 +39586,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.2">
+    <row r="109" spans="1:5" ht="31.5">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -39587,7 +39603,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.6">
+    <row r="110" spans="1:5" ht="15.75">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -39623,14 +39639,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41235,14 +41251,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41872,7 +41888,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -42955,14 +42971,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -44694,13 +44710,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46438,14 +46454,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="32"/>
+    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46584,7 +46600,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="46.8">
+    <row r="9" spans="1:5" ht="47.25">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -46601,7 +46617,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="46.8">
+    <row r="10" spans="1:5" ht="47.25">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -46652,7 +46668,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.2">
+    <row r="13" spans="1:5" ht="31.5">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -46720,7 +46736,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="46.8">
+    <row r="17" spans="1:5" ht="47.25">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -46771,7 +46787,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.2">
+    <row r="20" spans="1:5" ht="31.5">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -46805,7 +46821,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.2">
+    <row r="22" spans="1:5" ht="31.5">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -47026,7 +47042,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="62.4">
+    <row r="35" spans="1:5" ht="63">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -47094,7 +47110,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.2">
+    <row r="39" spans="1:5" ht="31.5">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47162,7 +47178,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.2">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -47366,7 +47382,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78">
+    <row r="55" spans="1:5" ht="78.75">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -47604,7 +47620,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.2">
+    <row r="69" spans="1:5" ht="31.5">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47672,7 +47688,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="62.4">
+    <row r="73" spans="1:5" ht="63">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -47918,7 +47934,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.2">
+    <row r="88" spans="1:5" ht="31.5">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -48020,7 +48036,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -48037,7 +48053,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -48071,7 +48087,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78">
+    <row r="97" spans="1:5" ht="78.75">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -48088,7 +48104,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -48139,7 +48155,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.2">
+    <row r="101" spans="1:5" ht="31.5">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -48258,7 +48274,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="62.4">
+    <row r="108" spans="1:5" ht="63">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -48329,14 +48345,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -49580,7 +49596,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="28.8">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -49869,7 +49885,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="43.2">
+    <row r="91" spans="1:5" ht="45">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -50107,7 +50123,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="72">
+    <row r="105" spans="1:5" ht="75">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -50124,7 +50140,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -50158,7 +50174,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="28.8">
+    <row r="108" spans="1:5" ht="30">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -50279,14 +50295,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51036,14 +51052,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51437,7 +51453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="28.8">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -51624,7 +51640,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="28.8">
+    <row r="35" spans="1:13" ht="30">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -51920,13 +51936,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -52014,7 +52030,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -52252,7 +52268,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" ht="30">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -52575,7 +52591,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="28.8">
+    <row r="39" spans="1:5" ht="30">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -52592,7 +52608,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -52609,7 +52625,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="28.8">
+    <row r="41" spans="1:5" ht="30">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -52626,7 +52642,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -52660,7 +52676,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -52898,7 +52914,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" ht="30">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -52915,7 +52931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="28.8">
+    <row r="59" spans="1:5" ht="30">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -53085,7 +53101,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -53170,7 +53186,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -53323,7 +53339,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" ht="30">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -53510,7 +53526,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" ht="30">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -53612,7 +53628,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" ht="30">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -53629,7 +53645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="28.8">
+    <row r="101" spans="1:5" ht="30">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -53782,7 +53798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -53799,7 +53815,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="28.8">
+    <row r="111" spans="1:5" ht="30">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -53884,7 +53900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -53935,7 +53951,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -54207,7 +54223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" ht="30">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -54360,7 +54376,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="28.8">
+    <row r="144" spans="1:5" ht="30">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -54428,7 +54444,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" ht="30">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -54462,7 +54478,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="28.8">
+    <row r="150" spans="1:5" ht="30">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -54479,7 +54495,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" ht="30">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -54734,7 +54750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" ht="30">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -54904,7 +54920,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" ht="30">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -54955,7 +54971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="28.8">
+    <row r="179" spans="1:5" ht="30">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -55040,7 +55056,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" ht="30">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -55125,7 +55141,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" ht="30">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -55703,7 +55719,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" ht="30">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -56063,12 +56079,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -56207,7 +56223,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -56734,7 +56750,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -57074,7 +57090,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="28.8">
+    <row r="60" spans="1:5" ht="30">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -57091,7 +57107,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="28.8">
+    <row r="61" spans="1:5" ht="30">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -57108,7 +57124,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="28.8">
+    <row r="62" spans="1:5" ht="30">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -57193,7 +57209,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -57346,7 +57362,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="28.8">
+    <row r="76" spans="1:5" ht="30">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -57363,7 +57379,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="28.8">
+    <row r="77" spans="1:5" ht="30">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -57414,7 +57430,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="28.8">
+    <row r="80" spans="1:5" ht="30">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -57536,12 +57552,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -58020,7 +58036,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" ht="30">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -58445,7 +58461,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>
@@ -58924,7 +58940,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="16" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="99" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>

--- a/data/states/nj/raw_download.xlsx
+++ b/data/states/nj/raw_download.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E52F3F1-84FF-4EC7-B610-F2B9C57D3588}"/>
+  <xr:revisionPtr revIDLastSave="121" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{825B2177-409A-43E2-9886-056AD711173D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7628" uniqueCount="3267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7632" uniqueCount="3268">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14242,6 +14242,9 @@
   </si>
   <si>
     <t>Grocery Delivery E-Services USA, Inc DBA Hello Fresh</t>
+  </si>
+  <si>
+    <t>8/19/26 - 11/15/26</t>
   </si>
 </sst>
 </file>
@@ -17141,6 +17144,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17755,7 +17762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -18343,7 +18350,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" ht="31.5">
       <c r="A35" s="48" t="s">
         <v>3114</v>
       </c>
@@ -19176,7 +19183,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="31.5">
+    <row r="84" spans="1:5" ht="47.25">
       <c r="A84" s="60" t="s">
         <v>3257</v>
       </c>
@@ -19312,7 +19319,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.5">
+    <row r="92" spans="1:5" ht="47.25">
       <c r="A92" s="60" t="s">
         <v>3266</v>
       </c>
@@ -19327,6 +19334,23 @@
       </c>
       <c r="E92" s="49">
         <v>374</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="60" t="s">
+        <v>2940</v>
+      </c>
+      <c r="B93" s="60" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C93" s="58" t="s">
+        <v>364</v>
+      </c>
+      <c r="D93" s="50" t="s">
+        <v>3267</v>
+      </c>
+      <c r="E93" s="49">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -38464,7 +38488,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.75">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -39586,7 +39610,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.5">
+    <row r="109" spans="1:5" ht="47.25">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -57535,7 +57559,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="19" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="16" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>
@@ -58940,7 +58964,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="99" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="15" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>

--- a/data/states/nj/raw_download.xlsx
+++ b/data/states/nj/raw_download.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="121" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{825B2177-409A-43E2-9886-056AD711173D}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E94C2CCC-92DB-41FD-A6F4-3A6D35F0EBA1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7632" uniqueCount="3268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7639" uniqueCount="3272">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14245,6 +14245,18 @@
   </si>
   <si>
     <t>8/19/26 - 11/15/26</t>
+  </si>
+  <si>
+    <t>Optum</t>
+  </si>
+  <si>
+    <t>Cenlar FSB</t>
+  </si>
+  <si>
+    <t>Ewing Twp.</t>
+  </si>
+  <si>
+    <t>8/21/26 - 10/30/26</t>
   </si>
 </sst>
 </file>
@@ -17762,7 +17774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -18350,7 +18362,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="31.5">
+    <row r="35" spans="1:5">
       <c r="A35" s="48" t="s">
         <v>3114</v>
       </c>
@@ -19183,7 +19195,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="47.25">
+    <row r="84" spans="1:5" ht="31.5">
       <c r="A84" s="60" t="s">
         <v>3257</v>
       </c>
@@ -19319,7 +19331,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="47.25">
+    <row r="92" spans="1:5" ht="31.5">
       <c r="A92" s="60" t="s">
         <v>3266</v>
       </c>
@@ -19351,6 +19363,40 @@
       </c>
       <c r="E93" s="49">
         <v>63</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="60" t="s">
+        <v>3268</v>
+      </c>
+      <c r="B94" s="60" t="s">
+        <v>2705</v>
+      </c>
+      <c r="C94" s="58" t="s">
+        <v>364</v>
+      </c>
+      <c r="D94" s="50">
+        <v>46363</v>
+      </c>
+      <c r="E94" s="49">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="60" t="s">
+        <v>3269</v>
+      </c>
+      <c r="B95" s="60" t="s">
+        <v>3270</v>
+      </c>
+      <c r="C95" s="58" t="s">
+        <v>364</v>
+      </c>
+      <c r="D95" s="50" t="s">
+        <v>3271</v>
+      </c>
+      <c r="E95" s="49">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -38488,7 +38534,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="15.75">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -39610,7 +39656,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="47.25">
+    <row r="109" spans="1:5" ht="31.5">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>

--- a/data/states/nj/raw_download.xlsx
+++ b/data/states/nj/raw_download.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/jesse_elliot_dol_nj_gov/Documents/Documents/Documents/Jesse Elliot/Communications Office/Websites/DOL/Revisions/8.28.26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E94C2CCC-92DB-41FD-A6F4-3A6D35F0EBA1}"/>
+  <xr:revisionPtr revIDLastSave="141" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C398B6E3-B4C4-4281-AEA0-07F39F2F97A9}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -57,6 +57,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'2019 WARN Notices'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'2020 WARN Notices'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'2021 WARN Notices'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'2026 WARN Notices'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -68,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7639" uniqueCount="3272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7643" uniqueCount="3275">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14257,6 +14258,15 @@
   </si>
   <si>
     <t>8/21/26 - 10/30/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enablx, INC </t>
+  </si>
+  <si>
+    <t>Rockaway Township</t>
+  </si>
+  <si>
+    <t>12/31/26 - 3/31/27</t>
   </si>
 </sst>
 </file>
@@ -17156,10 +17166,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17774,7 +17780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -18362,7 +18368,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" ht="31.5">
       <c r="A35" s="48" t="s">
         <v>3114</v>
       </c>
@@ -19195,7 +19201,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="31.5">
+    <row r="84" spans="1:5" ht="47.25">
       <c r="A84" s="60" t="s">
         <v>3257</v>
       </c>
@@ -19331,7 +19337,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.5">
+    <row r="92" spans="1:5" ht="47.25">
       <c r="A92" s="60" t="s">
         <v>3266</v>
       </c>
@@ -19397,6 +19403,23 @@
       </c>
       <c r="E95" s="49">
         <v>50</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="60" t="s">
+        <v>3272</v>
+      </c>
+      <c r="B96" s="60" t="s">
+        <v>3273</v>
+      </c>
+      <c r="C96" s="58" t="s">
+        <v>364</v>
+      </c>
+      <c r="D96" s="50" t="s">
+        <v>3274</v>
+      </c>
+      <c r="E96" s="49">
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -38534,7 +38557,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.75">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -39656,7 +39679,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.5">
+    <row r="109" spans="1:5" ht="47.25">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>

--- a/data/states/nj/raw_download.xlsx
+++ b/data/states/nj/raw_download.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/jesse_elliot_dol_nj_gov/Documents/Documents/Documents/Jesse Elliot/Communications Office/Websites/DOL/Revisions/8.28.26/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="141" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C398B6E3-B4C4-4281-AEA0-07F39F2F97A9}"/>
+  <xr:revisionPtr revIDLastSave="144" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24213DDD-46C0-4EF6-8923-2397CA5D6127}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -57,7 +57,6 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'2019 WARN Notices'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'2020 WARN Notices'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'2021 WARN Notices'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'2026 WARN Notices'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -69,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7643" uniqueCount="3275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7646" uniqueCount="3276">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14260,10 +14259,13 @@
     <t>8/21/26 - 10/30/26</t>
   </si>
   <si>
-    <t xml:space="preserve">Enablx, INC </t>
-  </si>
-  <si>
-    <t>Rockaway Township</t>
+    <t>Cellares Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enablx, Inc. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rockaway Twp. </t>
   </si>
   <si>
     <t>12/31/26 - 3/31/27</t>
@@ -17780,13 +17782,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E96"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <dimension ref="A1:E97"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17824,7 +17826,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.5">
+    <row r="3" spans="1:5" ht="31.2">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17875,7 +17877,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="47.25">
+    <row r="6" spans="1:5" ht="46.8">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17892,7 +17894,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="47.25">
+    <row r="7" spans="1:5" ht="46.8">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17909,7 +17911,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.5">
+    <row r="8" spans="1:5" ht="31.2">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17926,7 +17928,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17943,7 +17945,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78.75">
+    <row r="10" spans="1:5" ht="78">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -17994,7 +17996,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="47.25">
+    <row r="13" spans="1:5" ht="46.8">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -18011,7 +18013,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.5">
+    <row r="14" spans="1:5" ht="31.2">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -18096,7 +18098,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -18164,7 +18166,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="63">
+    <row r="23" spans="1:5" ht="62.4">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -18181,7 +18183,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.5">
+    <row r="24" spans="1:5" ht="31.2">
       <c r="A24" s="48" t="s">
         <v>3184</v>
       </c>
@@ -18198,7 +18200,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="47.25">
+    <row r="25" spans="1:5" ht="46.8">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18283,7 +18285,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.5">
+    <row r="30" spans="1:5" ht="31.2">
       <c r="A30" s="60" t="s">
         <v>3193</v>
       </c>
@@ -18368,7 +18370,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="31.5">
+    <row r="35" spans="1:5">
       <c r="A35" s="48" t="s">
         <v>3114</v>
       </c>
@@ -18589,7 +18591,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.5">
+    <row r="48" spans="1:5" ht="31.2">
       <c r="A48" s="48" t="s">
         <v>3217</v>
       </c>
@@ -18810,7 +18812,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="31.5">
+    <row r="61" spans="1:5" ht="31.2">
       <c r="A61" s="63" t="s">
         <v>3231</v>
       </c>
@@ -18878,7 +18880,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="31.5">
+    <row r="65" spans="1:5" ht="31.2">
       <c r="A65" s="63" t="s">
         <v>3235</v>
       </c>
@@ -18946,7 +18948,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.5">
+    <row r="69" spans="1:5" ht="31.2">
       <c r="A69" s="60" t="s">
         <v>3239</v>
       </c>
@@ -18997,7 +18999,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="31.5">
+    <row r="72" spans="1:5" ht="31.2">
       <c r="A72" s="60" t="s">
         <v>3243</v>
       </c>
@@ -19014,7 +19016,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="31.5">
+    <row r="73" spans="1:5" ht="31.2">
       <c r="A73" s="60" t="s">
         <v>3243</v>
       </c>
@@ -19031,7 +19033,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="31.5">
+    <row r="74" spans="1:5" ht="31.2">
       <c r="A74" s="63" t="s">
         <v>3244</v>
       </c>
@@ -19048,7 +19050,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="31.5">
+    <row r="75" spans="1:5" ht="31.2">
       <c r="A75" s="48" t="s">
         <v>3245</v>
       </c>
@@ -19082,7 +19084,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="63">
+    <row r="77" spans="1:5" ht="62.4">
       <c r="A77" s="60" t="s">
         <v>3248</v>
       </c>
@@ -19150,7 +19152,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.5">
+    <row r="81" spans="1:5" ht="31.2">
       <c r="A81" s="60" t="s">
         <v>3253</v>
       </c>
@@ -19201,7 +19203,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="47.25">
+    <row r="84" spans="1:5" ht="31.2">
       <c r="A84" s="60" t="s">
         <v>3257</v>
       </c>
@@ -19218,7 +19220,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="31.5">
+    <row r="85" spans="1:5" ht="31.2">
       <c r="A85" s="60" t="s">
         <v>3258</v>
       </c>
@@ -19235,7 +19237,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="31.5">
+    <row r="86" spans="1:5" ht="31.2">
       <c r="A86" s="60" t="s">
         <v>3243</v>
       </c>
@@ -19252,7 +19254,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="31.5">
+    <row r="87" spans="1:5" ht="31.2">
       <c r="A87" s="60" t="s">
         <v>3231</v>
       </c>
@@ -19337,7 +19339,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="47.25">
+    <row r="92" spans="1:5" ht="31.2">
       <c r="A92" s="60" t="s">
         <v>3266</v>
       </c>
@@ -19410,15 +19412,32 @@
         <v>3272</v>
       </c>
       <c r="B96" s="60" t="s">
-        <v>3273</v>
+        <v>1542</v>
       </c>
       <c r="C96" s="58" t="s">
         <v>364</v>
       </c>
-      <c r="D96" s="50" t="s">
+      <c r="D96" s="50">
+        <v>46345</v>
+      </c>
+      <c r="E96" s="49">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="60" t="s">
+        <v>3273</v>
+      </c>
+      <c r="B97" s="60" t="s">
         <v>3274</v>
       </c>
-      <c r="E96" s="49">
+      <c r="C97" s="58" t="s">
+        <v>364</v>
+      </c>
+      <c r="D97" s="50" t="s">
+        <v>3275</v>
+      </c>
+      <c r="E97" s="49">
         <v>187</v>
       </c>
     </row>
@@ -19438,12 +19457,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="50.88671875" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20398,7 +20417,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5" ht="28.8">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -20517,7 +20536,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="30">
+    <row r="64" spans="1:5" ht="28.8">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -20928,12 +20947,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="58.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20970,7 +20989,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30">
+    <row r="3" spans="1:5" ht="28.8">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -21004,7 +21023,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30">
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -21123,7 +21142,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30">
+    <row r="12" spans="1:5" ht="28.8">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -21191,7 +21210,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5" ht="28.8">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -21225,7 +21244,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -21667,7 +21686,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -21925,12 +21944,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -22035,7 +22054,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5" ht="28.8">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -22103,7 +22122,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="30">
+    <row r="11" spans="1:5" ht="28.8">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -22154,7 +22173,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="30">
+    <row r="14" spans="1:5" ht="28.8">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -22222,7 +22241,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -22596,7 +22615,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -22664,7 +22683,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -22834,7 +22853,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -23089,7 +23108,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -23480,7 +23499,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="30">
+    <row r="92" spans="1:5" ht="28.8">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -23548,7 +23567,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="30">
+    <row r="96" spans="1:5" ht="28.8">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -23650,7 +23669,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="45">
+    <row r="102" spans="1:5" ht="28.8">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -23667,7 +23686,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="30">
+    <row r="103" spans="1:5" ht="28.8">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -23718,7 +23737,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -23786,7 +23805,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5" ht="28.8">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -23820,7 +23839,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="30">
+    <row r="112" spans="1:5">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -23888,7 +23907,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5" ht="28.8">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -23922,7 +23941,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="30">
+    <row r="118" spans="1:5" ht="28.8">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -23939,7 +23958,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -24007,7 +24026,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="30">
+    <row r="123" spans="1:5">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -24143,7 +24162,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="30">
+    <row r="131" spans="1:5">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -24313,7 +24332,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="30">
+    <row r="141" spans="1:5" ht="28.8">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -24500,7 +24519,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="30">
+    <row r="152" spans="1:5">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -24843,13 +24862,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25906,7 +25925,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="30">
+    <row r="63" spans="1:5">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -25940,7 +25959,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -26059,7 +26078,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="30">
+    <row r="72" spans="1:5" ht="28.8">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -26093,7 +26112,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -26348,7 +26367,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="30">
+    <row r="89" spans="1:5" ht="28.8">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -26416,7 +26435,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="30">
+    <row r="93" spans="1:5" ht="28.8">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -26725,13 +26744,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -26853,7 +26872,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="30">
+    <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -27278,7 +27297,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="30">
+    <row r="33" spans="1:5" ht="28.8">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -27686,7 +27705,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -28029,13 +28048,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -28529,7 +28548,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -28903,7 +28922,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5" ht="28.8">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -29124,7 +29143,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -29158,7 +29177,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5" ht="28.8">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -29637,13 +29656,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -29663,7 +29682,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30">
+    <row r="2" spans="1:5" ht="28.8">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -29731,7 +29750,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -29782,7 +29801,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -29901,7 +29920,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -30037,7 +30056,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -30139,7 +30158,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -30156,7 +30175,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="30">
+    <row r="31" spans="1:5" ht="28.8">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -30173,7 +30192,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="45">
+    <row r="32" spans="1:5" ht="28.8">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -30275,7 +30294,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -30343,7 +30362,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -30513,7 +30532,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -30564,7 +30583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="30">
+    <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -30836,7 +30855,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="30">
+    <row r="71" spans="1:5" ht="28.8">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -31023,7 +31042,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="30">
+    <row r="82" spans="1:5" ht="28.8">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -31349,13 +31368,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -31460,7 +31479,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -33163,13 +33182,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -34294,7 +34313,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -34311,7 +34330,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="30">
+    <row r="68" spans="1:5">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -35365,7 +35384,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="30">
+    <row r="130" spans="1:5" ht="28.8">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -35424,13 +35443,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -37834,16 +37853,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" customWidth="1"/>
-    <col min="2" max="2" width="31.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.88671875" customWidth="1"/>
+    <col min="2" max="2" width="31.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75">
+    <row r="1" spans="1:5" ht="15.6">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -37860,7 +37879,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.5">
+    <row r="2" spans="1:5" ht="31.2">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37877,7 +37896,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75">
+    <row r="3" spans="1:5" ht="15.6">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -37894,7 +37913,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.5">
+    <row r="4" spans="1:5" ht="31.2">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -37911,7 +37930,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="47.25">
+    <row r="5" spans="1:5" ht="46.8">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -37928,7 +37947,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75">
+    <row r="6" spans="1:5" ht="15.6">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -37945,7 +37964,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75">
+    <row r="7" spans="1:5" ht="15.6">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -37962,7 +37981,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75">
+    <row r="8" spans="1:5" ht="15.6">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -37979,7 +37998,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -37996,7 +38015,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75">
+    <row r="10" spans="1:5" ht="15.6">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -38013,7 +38032,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.5">
+    <row r="11" spans="1:5" ht="31.2">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -38030,7 +38049,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="94.5">
+    <row r="12" spans="1:5" ht="93.6">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -38047,7 +38066,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75">
+    <row r="13" spans="1:5" ht="15.6">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -38064,7 +38083,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75">
+    <row r="14" spans="1:5" ht="15.6">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -38081,7 +38100,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75">
+    <row r="15" spans="1:5" ht="15.6">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -38098,7 +38117,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75">
+    <row r="16" spans="1:5" ht="15.6">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38115,7 +38134,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="63">
+    <row r="17" spans="1:5" ht="62.4">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -38132,7 +38151,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="63">
+    <row r="18" spans="1:5" ht="62.4">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -38149,7 +38168,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -38166,7 +38185,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75">
+    <row r="20" spans="1:5" ht="15.6">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -38183,7 +38202,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="47.25">
+    <row r="21" spans="1:5" ht="46.8">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -38200,7 +38219,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75">
+    <row r="22" spans="1:5" ht="15.6">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -38217,7 +38236,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75">
+    <row r="23" spans="1:5" ht="15.6">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -38234,7 +38253,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75">
+    <row r="24" spans="1:5" ht="15.6">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -38251,7 +38270,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75">
+    <row r="25" spans="1:5" ht="15.6">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -38268,7 +38287,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75">
+    <row r="26" spans="1:5" ht="15.6">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -38285,7 +38304,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.5">
+    <row r="27" spans="1:5" ht="31.2">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -38302,7 +38321,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75">
+    <row r="28" spans="1:5" ht="15.6">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -38319,7 +38338,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75">
+    <row r="29" spans="1:5" ht="15.6">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -38336,7 +38355,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75">
+    <row r="30" spans="1:5" ht="15.6">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -38353,7 +38372,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="94.5">
+    <row r="31" spans="1:5" ht="93.6">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38370,7 +38389,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="63">
+    <row r="32" spans="1:5" ht="62.4">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -38387,7 +38406,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75">
+    <row r="33" spans="1:5" ht="15.6">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -38404,7 +38423,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="63">
+    <row r="34" spans="1:5" ht="62.4">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -38421,7 +38440,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75">
+    <row r="35" spans="1:5" ht="15.6">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -38438,7 +38457,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.75">
+    <row r="36" spans="1:5" ht="15.6">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -38455,7 +38474,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75">
+    <row r="37" spans="1:5" ht="15.6">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -38472,7 +38491,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="63">
+    <row r="38" spans="1:5" ht="62.4">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -38489,7 +38508,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75">
+    <row r="39" spans="1:5" ht="15.6">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -38506,7 +38525,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.75">
+    <row r="40" spans="1:5" ht="15.6">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -38523,7 +38542,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75">
+    <row r="41" spans="1:5" ht="15.6">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -38540,7 +38559,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75">
+    <row r="42" spans="1:5" ht="15.6">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -38557,7 +38576,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="15.6">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -38574,7 +38593,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.75">
+    <row r="44" spans="1:5" ht="15.6">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -38591,7 +38610,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="47.25">
+    <row r="45" spans="1:5" ht="46.8">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -38608,7 +38627,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.75">
+    <row r="46" spans="1:5" ht="15.6">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -38625,7 +38644,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.75">
+    <row r="47" spans="1:5" ht="15.6">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -38642,7 +38661,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.5">
+    <row r="48" spans="1:5" ht="31.2">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -38659,7 +38678,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.75">
+    <row r="49" spans="1:5" ht="15.6">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -38676,7 +38695,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.5">
+    <row r="50" spans="1:5" ht="31.2">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38693,7 +38712,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.75">
+    <row r="51" spans="1:5" ht="15.6">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -38710,7 +38729,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.75">
+    <row r="52" spans="1:5" ht="15.6">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38727,7 +38746,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.75">
+    <row r="53" spans="1:5" ht="15.6">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -38744,7 +38763,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.5">
+    <row r="54" spans="1:5" ht="31.2">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38761,7 +38780,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.75">
+    <row r="55" spans="1:5" ht="15.6">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -38778,7 +38797,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="94.5">
+    <row r="56" spans="1:5" ht="93.6">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -38795,7 +38814,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.75">
+    <row r="57" spans="1:5" ht="15.6">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -38812,7 +38831,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.75">
+    <row r="58" spans="1:5" ht="15.6">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -38829,7 +38848,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.75">
+    <row r="59" spans="1:5" ht="15.6">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -38846,7 +38865,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.75">
+    <row r="60" spans="1:5" ht="15.6">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -38863,7 +38882,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="47.25">
+    <row r="61" spans="1:5" ht="46.8">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38880,7 +38899,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.75">
+    <row r="62" spans="1:5" ht="15.6">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -38897,7 +38916,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.75">
+    <row r="63" spans="1:5" ht="15.6">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -38914,7 +38933,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.75">
+    <row r="64" spans="1:5" ht="15.6">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -38931,7 +38950,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.75">
+    <row r="65" spans="1:5" ht="15.6">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38948,7 +38967,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.75">
+    <row r="66" spans="1:5" ht="15.6">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -38965,7 +38984,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.75">
+    <row r="67" spans="1:5" ht="15.6">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -38982,7 +39001,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.75">
+    <row r="68" spans="1:5" ht="15.6">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -38999,7 +39018,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.75">
+    <row r="69" spans="1:5" ht="15.6">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -39016,7 +39035,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.5">
+    <row r="70" spans="1:5" ht="31.2">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -39033,7 +39052,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.75">
+    <row r="71" spans="1:5" ht="15.6">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -39050,7 +39069,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.75">
+    <row r="72" spans="1:5" ht="15.6">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -39067,7 +39086,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.75">
+    <row r="73" spans="1:5" ht="15.6">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -39084,7 +39103,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="47.25">
+    <row r="74" spans="1:5" ht="46.8">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -39101,7 +39120,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.75">
+    <row r="75" spans="1:5" ht="15.6">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -39118,7 +39137,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.75">
+    <row r="76" spans="1:5" ht="15.6">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -39135,7 +39154,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.5">
+    <row r="77" spans="1:5" ht="31.2">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -39152,7 +39171,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.5">
+    <row r="78" spans="1:5" ht="31.2">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -39169,7 +39188,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.5">
+    <row r="79" spans="1:5" ht="31.2">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -39186,7 +39205,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.75">
+    <row r="80" spans="1:5" ht="15.6">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -39203,7 +39222,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.5">
+    <row r="81" spans="1:5" ht="31.2">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -39220,7 +39239,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.75">
+    <row r="82" spans="1:5" ht="15.6">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -39237,7 +39256,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.5">
+    <row r="83" spans="1:5" ht="31.2">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -39254,7 +39273,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="47.25">
+    <row r="84" spans="1:5" ht="46.8">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -39271,7 +39290,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.75">
+    <row r="85" spans="1:5" ht="15.6">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -39288,7 +39307,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.75">
+    <row r="86" spans="1:5" ht="15.6">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -39305,7 +39324,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.75">
+    <row r="87" spans="1:5" ht="15.6">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -39322,7 +39341,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.75">
+    <row r="88" spans="1:5" ht="15.6">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -39339,7 +39358,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.75">
+    <row r="89" spans="1:5" ht="15.6">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -39356,7 +39375,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.75">
+    <row r="90" spans="1:5" ht="15.6">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -39373,7 +39392,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="47.25">
+    <row r="91" spans="1:5" ht="46.8">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -39390,7 +39409,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.5">
+    <row r="92" spans="1:5" ht="31.2">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -39407,7 +39426,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.5">
+    <row r="93" spans="1:5" ht="31.2">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -39424,7 +39443,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -39441,7 +39460,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -39458,7 +39477,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.75">
+    <row r="96" spans="1:5" ht="15.6">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -39475,7 +39494,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.75">
+    <row r="97" spans="1:5" ht="15.6">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -39492,7 +39511,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -39509,7 +39528,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.5">
+    <row r="99" spans="1:5" ht="31.2">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -39526,7 +39545,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.75">
+    <row r="100" spans="1:5" ht="15.6">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -39543,7 +39562,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.75">
+    <row r="101" spans="1:5" ht="15.6">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -39560,7 +39579,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.5">
+    <row r="102" spans="1:5" ht="31.2">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -39577,7 +39596,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.75">
+    <row r="103" spans="1:5" ht="15.6">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -39594,7 +39613,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.75">
+    <row r="104" spans="1:5" ht="15.6">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -39611,7 +39630,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.75">
+    <row r="105" spans="1:5" ht="15.6">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -39628,7 +39647,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.75">
+    <row r="106" spans="1:5" ht="15.6">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -39645,7 +39664,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.75">
+    <row r="107" spans="1:5" ht="15.6">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -39662,7 +39681,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.75">
+    <row r="108" spans="1:5" ht="15.6">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -39679,7 +39698,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="47.25">
+    <row r="109" spans="1:5" ht="31.2">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -39696,7 +39715,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.75">
+    <row r="110" spans="1:5" ht="15.6">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -39732,14 +39751,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41344,14 +41363,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41981,7 +42000,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -43064,14 +43083,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -44803,13 +44822,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46547,14 +46566,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="32"/>
+    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46693,7 +46712,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="47.25">
+    <row r="9" spans="1:5" ht="46.8">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -46710,7 +46729,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="47.25">
+    <row r="10" spans="1:5" ht="46.8">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -46761,7 +46780,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.5">
+    <row r="13" spans="1:5" ht="31.2">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -46829,7 +46848,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="47.25">
+    <row r="17" spans="1:5" ht="46.8">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -46880,7 +46899,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.5">
+    <row r="20" spans="1:5" ht="31.2">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -46914,7 +46933,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.5">
+    <row r="22" spans="1:5" ht="31.2">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -47135,7 +47154,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="63">
+    <row r="35" spans="1:5" ht="62.4">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -47203,7 +47222,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.5">
+    <row r="39" spans="1:5" ht="31.2">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47271,7 +47290,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="31.2">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -47475,7 +47494,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78.75">
+    <row r="55" spans="1:5" ht="78">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -47713,7 +47732,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.5">
+    <row r="69" spans="1:5" ht="31.2">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47781,7 +47800,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="63">
+    <row r="73" spans="1:5" ht="62.4">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -48027,7 +48046,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.5">
+    <row r="88" spans="1:5" ht="31.2">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -48129,7 +48148,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -48146,7 +48165,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -48180,7 +48199,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78.75">
+    <row r="97" spans="1:5" ht="78">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -48197,7 +48216,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -48248,7 +48267,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.5">
+    <row r="101" spans="1:5" ht="31.2">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -48367,7 +48386,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="63">
+    <row r="108" spans="1:5" ht="62.4">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -48438,14 +48457,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -49689,7 +49708,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5" ht="28.8">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -49978,7 +49997,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="45">
+    <row r="91" spans="1:5" ht="43.2">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -50216,7 +50235,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="75">
+    <row r="105" spans="1:5" ht="72">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -50233,7 +50252,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -50267,7 +50286,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="30">
+    <row r="108" spans="1:5" ht="28.8">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -50388,14 +50407,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51145,14 +51164,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51546,7 +51565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5" ht="28.8">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -51733,7 +51752,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="30">
+    <row r="35" spans="1:13" ht="28.8">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -52029,13 +52048,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -52123,7 +52142,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -52361,7 +52380,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="30">
+    <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -52684,7 +52703,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="30">
+    <row r="39" spans="1:5" ht="28.8">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -52701,7 +52720,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -52718,7 +52737,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="30">
+    <row r="41" spans="1:5" ht="28.8">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -52735,7 +52754,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -52769,7 +52788,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -53007,7 +53026,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="30">
+    <row r="58" spans="1:5">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -53024,7 +53043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="30">
+    <row r="59" spans="1:5" ht="28.8">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -53194,7 +53213,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -53279,7 +53298,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -53432,7 +53451,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="30">
+    <row r="83" spans="1:5">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -53619,7 +53638,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="30">
+    <row r="94" spans="1:5">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -53721,7 +53740,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="30">
+    <row r="100" spans="1:5">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -53738,7 +53757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="30">
+    <row r="101" spans="1:5" ht="28.8">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -53891,7 +53910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -53908,7 +53927,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="30">
+    <row r="111" spans="1:5" ht="28.8">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -53993,7 +54012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -54044,7 +54063,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -54316,7 +54335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="30">
+    <row r="135" spans="1:5">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -54469,7 +54488,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="30">
+    <row r="144" spans="1:5" ht="28.8">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -54537,7 +54556,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="30">
+    <row r="148" spans="1:5">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -54571,7 +54590,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="30">
+    <row r="150" spans="1:5" ht="28.8">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -54588,7 +54607,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="30">
+    <row r="151" spans="1:5">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -54843,7 +54862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="30">
+    <row r="166" spans="1:5">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -55013,7 +55032,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="30">
+    <row r="176" spans="1:5">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -55064,7 +55083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="30">
+    <row r="179" spans="1:5" ht="28.8">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -55149,7 +55168,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="30">
+    <row r="184" spans="1:5">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -55234,7 +55253,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="30">
+    <row r="189" spans="1:5">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -55812,7 +55831,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="30">
+    <row r="223" spans="1:5">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -56172,12 +56191,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -56316,7 +56335,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -56843,7 +56862,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -57183,7 +57202,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="30">
+    <row r="60" spans="1:5" ht="28.8">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -57200,7 +57219,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="30">
+    <row r="61" spans="1:5" ht="28.8">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -57217,7 +57236,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="30">
+    <row r="62" spans="1:5" ht="28.8">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -57302,7 +57321,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -57455,7 +57474,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="30">
+    <row r="76" spans="1:5" ht="28.8">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -57472,7 +57491,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="30">
+    <row r="77" spans="1:5" ht="28.8">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -57523,7 +57542,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="30">
+    <row r="80" spans="1:5" ht="28.8">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -57628,7 +57647,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="16" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="40" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>
@@ -57645,12 +57664,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -58129,7 +58148,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="30">
+    <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -58554,7 +58573,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>
@@ -59033,7 +59052,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="15" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="20" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>

--- a/data/states/nj/raw_download.xlsx
+++ b/data/states/nj/raw_download.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="144" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24213DDD-46C0-4EF6-8923-2397CA5D6127}"/>
+  <xr:revisionPtr revIDLastSave="145" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2613A98-5DFA-41A8-B280-2938AA589FA3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7646" uniqueCount="3276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7650" uniqueCount="3277">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14269,6 +14269,9 @@
   </si>
   <si>
     <t>12/31/26 - 3/31/27</t>
+  </si>
+  <si>
+    <t>11/25/26  - 11/30/26</t>
   </si>
 </sst>
 </file>
@@ -17168,6 +17171,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17782,13 +17789,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E97"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <dimension ref="A1:E98"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.33203125" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17826,7 +17833,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.2">
+    <row r="3" spans="1:5" ht="31.5">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17877,7 +17884,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="46.8">
+    <row r="6" spans="1:5" ht="47.25">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17894,7 +17901,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="46.8">
+    <row r="7" spans="1:5" ht="47.25">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17911,7 +17918,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.2">
+    <row r="8" spans="1:5" ht="31.5">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17928,7 +17935,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17945,7 +17952,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78">
+    <row r="10" spans="1:5" ht="78.75">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -17996,7 +18003,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="46.8">
+    <row r="13" spans="1:5" ht="47.25">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -18013,7 +18020,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.2">
+    <row r="14" spans="1:5" ht="31.5">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -18098,7 +18105,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -18166,7 +18173,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="62.4">
+    <row r="23" spans="1:5" ht="63">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -18183,7 +18190,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.2">
+    <row r="24" spans="1:5" ht="31.5">
       <c r="A24" s="48" t="s">
         <v>3184</v>
       </c>
@@ -18200,7 +18207,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="46.8">
+    <row r="25" spans="1:5" ht="47.25">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18285,7 +18292,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.2">
+    <row r="30" spans="1:5" ht="31.5">
       <c r="A30" s="60" t="s">
         <v>3193</v>
       </c>
@@ -18370,7 +18377,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" ht="31.5">
       <c r="A35" s="48" t="s">
         <v>3114</v>
       </c>
@@ -18591,7 +18598,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.2">
+    <row r="48" spans="1:5" ht="31.5">
       <c r="A48" s="48" t="s">
         <v>3217</v>
       </c>
@@ -18812,7 +18819,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="31.2">
+    <row r="61" spans="1:5" ht="31.5">
       <c r="A61" s="63" t="s">
         <v>3231</v>
       </c>
@@ -18880,7 +18887,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="31.2">
+    <row r="65" spans="1:5" ht="31.5">
       <c r="A65" s="63" t="s">
         <v>3235</v>
       </c>
@@ -18948,7 +18955,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.2">
+    <row r="69" spans="1:5" ht="31.5">
       <c r="A69" s="60" t="s">
         <v>3239</v>
       </c>
@@ -18999,7 +19006,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="31.2">
+    <row r="72" spans="1:5" ht="31.5">
       <c r="A72" s="60" t="s">
         <v>3243</v>
       </c>
@@ -19016,7 +19023,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="31.2">
+    <row r="73" spans="1:5" ht="31.5">
       <c r="A73" s="60" t="s">
         <v>3243</v>
       </c>
@@ -19033,7 +19040,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="31.2">
+    <row r="74" spans="1:5" ht="31.5">
       <c r="A74" s="63" t="s">
         <v>3244</v>
       </c>
@@ -19050,7 +19057,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="31.2">
+    <row r="75" spans="1:5" ht="31.5">
       <c r="A75" s="48" t="s">
         <v>3245</v>
       </c>
@@ -19084,7 +19091,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="62.4">
+    <row r="77" spans="1:5" ht="63">
       <c r="A77" s="60" t="s">
         <v>3248</v>
       </c>
@@ -19152,7 +19159,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.2">
+    <row r="81" spans="1:5" ht="31.5">
       <c r="A81" s="60" t="s">
         <v>3253</v>
       </c>
@@ -19203,7 +19210,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="31.2">
+    <row r="84" spans="1:5" ht="47.25">
       <c r="A84" s="60" t="s">
         <v>3257</v>
       </c>
@@ -19220,7 +19227,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="31.2">
+    <row r="85" spans="1:5" ht="31.5">
       <c r="A85" s="60" t="s">
         <v>3258</v>
       </c>
@@ -19237,7 +19244,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="31.2">
+    <row r="86" spans="1:5" ht="31.5">
       <c r="A86" s="60" t="s">
         <v>3243</v>
       </c>
@@ -19254,7 +19261,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="31.2">
+    <row r="87" spans="1:5" ht="31.5">
       <c r="A87" s="60" t="s">
         <v>3231</v>
       </c>
@@ -19339,7 +19346,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.2">
+    <row r="92" spans="1:5" ht="47.25">
       <c r="A92" s="60" t="s">
         <v>3266</v>
       </c>
@@ -19439,6 +19446,23 @@
       </c>
       <c r="E97" s="49">
         <v>187</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="48" t="s">
+        <v>3204</v>
+      </c>
+      <c r="B98" s="48" t="s">
+        <v>2694</v>
+      </c>
+      <c r="C98" s="49" t="s">
+        <v>394</v>
+      </c>
+      <c r="D98" s="50" t="s">
+        <v>3276</v>
+      </c>
+      <c r="E98" s="48">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -19457,12 +19481,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="50.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20417,7 +20441,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="28.8">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -20536,7 +20560,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="28.8">
+    <row r="64" spans="1:5" ht="30">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -20947,12 +20971,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.88671875" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="58.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20989,7 +21013,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.8">
+    <row r="3" spans="1:5" ht="30">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -21023,7 +21047,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="30">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -21142,7 +21166,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="28.8">
+    <row r="12" spans="1:5" ht="30">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -21210,7 +21234,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="28.8">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -21244,7 +21268,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -21686,7 +21710,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -21944,12 +21968,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -22054,7 +22078,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="28.8">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -22122,7 +22146,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="28.8">
+    <row r="11" spans="1:5" ht="30">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -22173,7 +22197,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="28.8">
+    <row r="14" spans="1:5" ht="30">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -22241,7 +22265,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -22615,7 +22639,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -22683,7 +22707,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -22853,7 +22877,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -23108,7 +23132,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -23499,7 +23523,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="28.8">
+    <row r="92" spans="1:5" ht="30">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -23567,7 +23591,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="28.8">
+    <row r="96" spans="1:5" ht="30">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -23669,7 +23693,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="28.8">
+    <row r="102" spans="1:5" ht="45">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -23686,7 +23710,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="28.8">
+    <row r="103" spans="1:5" ht="30">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -23737,7 +23761,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -23805,7 +23829,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="28.8">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -23839,7 +23863,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" ht="30">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -23907,7 +23931,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="28.8">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -23941,7 +23965,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="28.8">
+    <row r="118" spans="1:5" ht="30">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -23958,7 +23982,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -24026,7 +24050,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" ht="30">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -24162,7 +24186,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" ht="30">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -24332,7 +24356,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="28.8">
+    <row r="141" spans="1:5" ht="30">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -24519,7 +24543,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" ht="30">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -24862,13 +24886,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25925,7 +25949,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" ht="30">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -25959,7 +25983,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -26078,7 +26102,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="28.8">
+    <row r="72" spans="1:5" ht="30">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -26112,7 +26136,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -26367,7 +26391,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="28.8">
+    <row r="89" spans="1:5" ht="30">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -26435,7 +26459,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="28.8">
+    <row r="93" spans="1:5" ht="30">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -26744,13 +26768,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -26872,7 +26896,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" ht="30">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -27297,7 +27321,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="28.8">
+    <row r="33" spans="1:5" ht="30">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -27705,7 +27729,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -28048,13 +28072,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -28548,7 +28572,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -28922,7 +28946,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="28.8">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -29143,7 +29167,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -29177,7 +29201,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="28.8">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -29656,13 +29680,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -29682,7 +29706,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8">
+    <row r="2" spans="1:5" ht="30">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -29750,7 +29774,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -29801,7 +29825,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -29920,7 +29944,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -30056,7 +30080,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -30158,7 +30182,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -30175,7 +30199,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="28.8">
+    <row r="31" spans="1:5" ht="30">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -30192,7 +30216,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="28.8">
+    <row r="32" spans="1:5" ht="45">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -30294,7 +30318,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -30362,7 +30386,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -30532,7 +30556,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -30583,7 +30607,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" ht="30">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -30855,7 +30879,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="28.8">
+    <row r="71" spans="1:5" ht="30">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -31042,7 +31066,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="28.8">
+    <row r="82" spans="1:5" ht="30">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -31368,13 +31392,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -31479,7 +31503,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -33182,13 +33206,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -34313,7 +34337,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -34330,7 +34354,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" ht="30">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -35384,7 +35408,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="28.8">
+    <row r="130" spans="1:5" ht="30">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -35443,13 +35467,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -37853,16 +37877,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.88671875" customWidth="1"/>
-    <col min="2" max="2" width="31.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="28.33203125" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="31.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="28.28515625" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6">
+    <row r="1" spans="1:5" ht="15.75">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -37879,7 +37903,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.2">
+    <row r="2" spans="1:5" ht="31.5">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37896,7 +37920,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.6">
+    <row r="3" spans="1:5" ht="15.75">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -37913,7 +37937,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.2">
+    <row r="4" spans="1:5" ht="31.5">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -37930,7 +37954,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="46.8">
+    <row r="5" spans="1:5" ht="47.25">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -37947,7 +37971,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.6">
+    <row r="6" spans="1:5" ht="15.75">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -37964,7 +37988,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.6">
+    <row r="7" spans="1:5" ht="15.75">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -37981,7 +38005,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.6">
+    <row r="8" spans="1:5" ht="15.75">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -37998,7 +38022,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -38015,7 +38039,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.6">
+    <row r="10" spans="1:5" ht="15.75">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -38032,7 +38056,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.2">
+    <row r="11" spans="1:5" ht="31.5">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -38049,7 +38073,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="93.6">
+    <row r="12" spans="1:5" ht="94.5">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -38066,7 +38090,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.6">
+    <row r="13" spans="1:5" ht="15.75">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -38083,7 +38107,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.6">
+    <row r="14" spans="1:5" ht="15.75">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -38100,7 +38124,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.6">
+    <row r="15" spans="1:5" ht="15.75">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -38117,7 +38141,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.6">
+    <row r="16" spans="1:5" ht="15.75">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38134,7 +38158,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="62.4">
+    <row r="17" spans="1:5" ht="63">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -38151,7 +38175,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="62.4">
+    <row r="18" spans="1:5" ht="63">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -38168,7 +38192,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -38185,7 +38209,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.6">
+    <row r="20" spans="1:5" ht="15.75">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -38202,7 +38226,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="46.8">
+    <row r="21" spans="1:5" ht="47.25">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -38219,7 +38243,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.6">
+    <row r="22" spans="1:5" ht="15.75">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -38236,7 +38260,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.6">
+    <row r="23" spans="1:5" ht="15.75">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -38253,7 +38277,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.6">
+    <row r="24" spans="1:5" ht="15.75">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -38270,7 +38294,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.6">
+    <row r="25" spans="1:5" ht="15.75">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -38287,7 +38311,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.6">
+    <row r="26" spans="1:5" ht="15.75">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -38304,7 +38328,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.2">
+    <row r="27" spans="1:5" ht="31.5">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -38321,7 +38345,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.6">
+    <row r="28" spans="1:5" ht="15.75">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -38338,7 +38362,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.6">
+    <row r="29" spans="1:5" ht="15.75">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -38355,7 +38379,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.6">
+    <row r="30" spans="1:5" ht="15.75">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -38372,7 +38396,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="93.6">
+    <row r="31" spans="1:5" ht="94.5">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38389,7 +38413,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="62.4">
+    <row r="32" spans="1:5" ht="63">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -38406,7 +38430,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.6">
+    <row r="33" spans="1:5" ht="15.75">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -38423,7 +38447,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="62.4">
+    <row r="34" spans="1:5" ht="63">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -38440,7 +38464,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.6">
+    <row r="35" spans="1:5" ht="15.75">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -38457,7 +38481,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.6">
+    <row r="36" spans="1:5" ht="15.75">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -38474,7 +38498,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.6">
+    <row r="37" spans="1:5" ht="15.75">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -38491,7 +38515,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="62.4">
+    <row r="38" spans="1:5" ht="63">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -38508,7 +38532,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.6">
+    <row r="39" spans="1:5" ht="15.75">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -38525,7 +38549,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.6">
+    <row r="40" spans="1:5" ht="15.75">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -38542,7 +38566,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.6">
+    <row r="41" spans="1:5" ht="15.75">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -38559,7 +38583,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.6">
+    <row r="42" spans="1:5" ht="15.75">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -38576,7 +38600,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.6">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -38593,7 +38617,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.6">
+    <row r="44" spans="1:5" ht="15.75">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -38610,7 +38634,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="46.8">
+    <row r="45" spans="1:5" ht="47.25">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -38627,7 +38651,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.6">
+    <row r="46" spans="1:5" ht="15.75">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -38644,7 +38668,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.6">
+    <row r="47" spans="1:5" ht="15.75">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -38661,7 +38685,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.2">
+    <row r="48" spans="1:5" ht="31.5">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -38678,7 +38702,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.6">
+    <row r="49" spans="1:5" ht="15.75">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -38695,7 +38719,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.2">
+    <row r="50" spans="1:5" ht="31.5">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38712,7 +38736,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.6">
+    <row r="51" spans="1:5" ht="15.75">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -38729,7 +38753,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.6">
+    <row r="52" spans="1:5" ht="15.75">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38746,7 +38770,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.6">
+    <row r="53" spans="1:5" ht="15.75">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -38763,7 +38787,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.2">
+    <row r="54" spans="1:5" ht="31.5">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38780,7 +38804,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.6">
+    <row r="55" spans="1:5" ht="15.75">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -38797,7 +38821,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="93.6">
+    <row r="56" spans="1:5" ht="94.5">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -38814,7 +38838,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.6">
+    <row r="57" spans="1:5" ht="15.75">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -38831,7 +38855,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.6">
+    <row r="58" spans="1:5" ht="15.75">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -38848,7 +38872,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.6">
+    <row r="59" spans="1:5" ht="15.75">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -38865,7 +38889,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.6">
+    <row r="60" spans="1:5" ht="15.75">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -38882,7 +38906,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="46.8">
+    <row r="61" spans="1:5" ht="47.25">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38899,7 +38923,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.6">
+    <row r="62" spans="1:5" ht="15.75">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -38916,7 +38940,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.6">
+    <row r="63" spans="1:5" ht="15.75">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -38933,7 +38957,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.6">
+    <row r="64" spans="1:5" ht="15.75">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -38950,7 +38974,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.6">
+    <row r="65" spans="1:5" ht="15.75">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38967,7 +38991,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.6">
+    <row r="66" spans="1:5" ht="15.75">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -38984,7 +39008,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.6">
+    <row r="67" spans="1:5" ht="15.75">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -39001,7 +39025,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.6">
+    <row r="68" spans="1:5" ht="15.75">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -39018,7 +39042,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.6">
+    <row r="69" spans="1:5" ht="15.75">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -39035,7 +39059,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.2">
+    <row r="70" spans="1:5" ht="31.5">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -39052,7 +39076,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.6">
+    <row r="71" spans="1:5" ht="15.75">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -39069,7 +39093,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.6">
+    <row r="72" spans="1:5" ht="15.75">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -39086,7 +39110,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.6">
+    <row r="73" spans="1:5" ht="15.75">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -39103,7 +39127,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="46.8">
+    <row r="74" spans="1:5" ht="47.25">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -39120,7 +39144,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.6">
+    <row r="75" spans="1:5" ht="15.75">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -39137,7 +39161,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.6">
+    <row r="76" spans="1:5" ht="15.75">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -39154,7 +39178,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.2">
+    <row r="77" spans="1:5" ht="31.5">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -39171,7 +39195,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.2">
+    <row r="78" spans="1:5" ht="31.5">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -39188,7 +39212,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.2">
+    <row r="79" spans="1:5" ht="31.5">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -39205,7 +39229,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.6">
+    <row r="80" spans="1:5" ht="15.75">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -39222,7 +39246,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.2">
+    <row r="81" spans="1:5" ht="31.5">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -39239,7 +39263,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.6">
+    <row r="82" spans="1:5" ht="15.75">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -39256,7 +39280,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.2">
+    <row r="83" spans="1:5" ht="31.5">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -39273,7 +39297,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="46.8">
+    <row r="84" spans="1:5" ht="47.25">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -39290,7 +39314,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.6">
+    <row r="85" spans="1:5" ht="15.75">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -39307,7 +39331,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.6">
+    <row r="86" spans="1:5" ht="15.75">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -39324,7 +39348,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.6">
+    <row r="87" spans="1:5" ht="15.75">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -39341,7 +39365,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.6">
+    <row r="88" spans="1:5" ht="15.75">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -39358,7 +39382,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.6">
+    <row r="89" spans="1:5" ht="15.75">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -39375,7 +39399,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.6">
+    <row r="90" spans="1:5" ht="15.75">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -39392,7 +39416,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="46.8">
+    <row r="91" spans="1:5" ht="47.25">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -39409,7 +39433,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.2">
+    <row r="92" spans="1:5" ht="31.5">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -39426,7 +39450,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.2">
+    <row r="93" spans="1:5" ht="31.5">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -39443,7 +39467,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -39460,7 +39484,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -39477,7 +39501,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.6">
+    <row r="96" spans="1:5" ht="15.75">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -39494,7 +39518,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.6">
+    <row r="97" spans="1:5" ht="15.75">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -39511,7 +39535,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -39528,7 +39552,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.2">
+    <row r="99" spans="1:5" ht="31.5">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -39545,7 +39569,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.6">
+    <row r="100" spans="1:5" ht="15.75">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -39562,7 +39586,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.6">
+    <row r="101" spans="1:5" ht="15.75">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -39579,7 +39603,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.2">
+    <row r="102" spans="1:5" ht="31.5">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -39596,7 +39620,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.6">
+    <row r="103" spans="1:5" ht="15.75">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -39613,7 +39637,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.6">
+    <row r="104" spans="1:5" ht="15.75">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -39630,7 +39654,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.6">
+    <row r="105" spans="1:5" ht="15.75">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -39647,7 +39671,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.6">
+    <row r="106" spans="1:5" ht="15.75">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -39664,7 +39688,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.6">
+    <row r="107" spans="1:5" ht="15.75">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -39681,7 +39705,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.6">
+    <row r="108" spans="1:5" ht="15.75">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -39698,7 +39722,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.2">
+    <row r="109" spans="1:5" ht="47.25">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -39715,7 +39739,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.6">
+    <row r="110" spans="1:5" ht="15.75">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -39751,14 +39775,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41363,14 +41387,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -42000,7 +42024,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -43083,14 +43107,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -44822,13 +44846,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46566,14 +46590,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="32"/>
+    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46712,7 +46736,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="46.8">
+    <row r="9" spans="1:5" ht="47.25">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -46729,7 +46753,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="46.8">
+    <row r="10" spans="1:5" ht="47.25">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -46780,7 +46804,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.2">
+    <row r="13" spans="1:5" ht="31.5">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -46848,7 +46872,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="46.8">
+    <row r="17" spans="1:5" ht="47.25">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -46899,7 +46923,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.2">
+    <row r="20" spans="1:5" ht="31.5">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -46933,7 +46957,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.2">
+    <row r="22" spans="1:5" ht="31.5">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -47154,7 +47178,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="62.4">
+    <row r="35" spans="1:5" ht="63">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -47222,7 +47246,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.2">
+    <row r="39" spans="1:5" ht="31.5">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47290,7 +47314,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.2">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -47494,7 +47518,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78">
+    <row r="55" spans="1:5" ht="78.75">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -47732,7 +47756,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.2">
+    <row r="69" spans="1:5" ht="31.5">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47800,7 +47824,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="62.4">
+    <row r="73" spans="1:5" ht="63">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -48046,7 +48070,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.2">
+    <row r="88" spans="1:5" ht="31.5">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -48148,7 +48172,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -48165,7 +48189,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -48199,7 +48223,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78">
+    <row r="97" spans="1:5" ht="78.75">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -48216,7 +48240,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -48267,7 +48291,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.2">
+    <row r="101" spans="1:5" ht="31.5">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -48386,7 +48410,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="62.4">
+    <row r="108" spans="1:5" ht="63">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -48457,14 +48481,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -49708,7 +49732,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="28.8">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -49997,7 +50021,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="43.2">
+    <row r="91" spans="1:5" ht="45">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -50235,7 +50259,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="72">
+    <row r="105" spans="1:5" ht="75">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -50252,7 +50276,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -50286,7 +50310,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="28.8">
+    <row r="108" spans="1:5" ht="30">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -50407,14 +50431,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51164,14 +51188,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51565,7 +51589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="28.8">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -51752,7 +51776,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="28.8">
+    <row r="35" spans="1:13" ht="30">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -52048,13 +52072,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -52142,7 +52166,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -52380,7 +52404,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" ht="30">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -52703,7 +52727,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="28.8">
+    <row r="39" spans="1:5" ht="30">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -52720,7 +52744,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -52737,7 +52761,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="28.8">
+    <row r="41" spans="1:5" ht="30">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -52754,7 +52778,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -52788,7 +52812,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -53026,7 +53050,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" ht="30">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -53043,7 +53067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="28.8">
+    <row r="59" spans="1:5" ht="30">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -53213,7 +53237,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -53298,7 +53322,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -53451,7 +53475,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" ht="30">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -53638,7 +53662,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" ht="30">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -53740,7 +53764,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" ht="30">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -53757,7 +53781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="28.8">
+    <row r="101" spans="1:5" ht="30">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -53910,7 +53934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -53927,7 +53951,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="28.8">
+    <row r="111" spans="1:5" ht="30">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -54012,7 +54036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -54063,7 +54087,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -54335,7 +54359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" ht="30">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -54488,7 +54512,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="28.8">
+    <row r="144" spans="1:5" ht="30">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -54556,7 +54580,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" ht="30">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -54590,7 +54614,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="28.8">
+    <row r="150" spans="1:5" ht="30">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -54607,7 +54631,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" ht="30">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -54862,7 +54886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" ht="30">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -55032,7 +55056,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" ht="30">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -55083,7 +55107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="28.8">
+    <row r="179" spans="1:5" ht="30">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -55168,7 +55192,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" ht="30">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -55253,7 +55277,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" ht="30">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -55831,7 +55855,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" ht="30">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -56191,12 +56215,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -56335,7 +56359,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -56862,7 +56886,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -57202,7 +57226,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="28.8">
+    <row r="60" spans="1:5" ht="30">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -57219,7 +57243,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="28.8">
+    <row r="61" spans="1:5" ht="30">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -57236,7 +57260,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="28.8">
+    <row r="62" spans="1:5" ht="30">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -57321,7 +57345,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -57474,7 +57498,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="28.8">
+    <row r="76" spans="1:5" ht="30">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -57491,7 +57515,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="28.8">
+    <row r="77" spans="1:5" ht="30">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -57542,7 +57566,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="28.8">
+    <row r="80" spans="1:5" ht="30">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -57664,12 +57688,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -58148,7 +58172,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" ht="30">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -58573,7 +58597,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>

--- a/data/states/nj/raw_download.xlsx
+++ b/data/states/nj/raw_download.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="145" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2613A98-5DFA-41A8-B280-2938AA589FA3}"/>
+  <xr:revisionPtr revIDLastSave="151" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3B5226D-C155-4125-AFC6-492D4BEDE01F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7650" uniqueCount="3277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7654" uniqueCount="3278">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14272,6 +14272,9 @@
   </si>
   <si>
     <t>11/25/26  - 11/30/26</t>
+  </si>
+  <si>
+    <t>12/11/26 and 1/4/27</t>
   </si>
 </sst>
 </file>
@@ -17171,10 +17174,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17789,7 +17788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -19463,6 +19462,23 @@
       </c>
       <c r="E98" s="48">
         <v>41</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="60" t="s">
+        <v>3234</v>
+      </c>
+      <c r="B99" s="60" t="s">
+        <v>3066</v>
+      </c>
+      <c r="C99" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="D99" s="50" t="s">
+        <v>3277</v>
+      </c>
+      <c r="E99" s="49">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -57671,7 +57687,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="40" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="16" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>
@@ -59076,7 +59092,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="20" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="15" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>

--- a/data/states/nj/raw_download.xlsx
+++ b/data/states/nj/raw_download.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="151" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3B5226D-C155-4125-AFC6-492D4BEDE01F}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E536ABD9-EB31-4E9B-B5CF-8E452BFDD949}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7654" uniqueCount="3278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7658" uniqueCount="3280">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14275,6 +14275,12 @@
   </si>
   <si>
     <t>12/11/26 and 1/4/27</t>
+  </si>
+  <si>
+    <t>Educational Testing Service</t>
+  </si>
+  <si>
+    <t>11/9/26 and 12/31/26</t>
   </si>
 </sst>
 </file>
@@ -17174,6 +17180,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17788,7 +17798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -19479,6 +19489,23 @@
       </c>
       <c r="E99" s="49">
         <v>54</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="31.5">
+      <c r="A100" s="60" t="s">
+        <v>3278</v>
+      </c>
+      <c r="B100" s="60" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C100" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="D100" s="50" t="s">
+        <v>3279</v>
+      </c>
+      <c r="E100" s="49">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
